--- a/LINE_Bot_內容對照表.xlsx
+++ b/LINE_Bot_內容對照表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0560D7A-BA3E-4DF2-89F5-1222224EFCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF35EAF-C88B-44D2-AB4C-385B81133ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="473">
   <si>
     <t>欄位說明</t>
   </si>
@@ -11632,6 +11632,21 @@
   <si>
     <t>檔案應用其他綜合業務諮詢.png</t>
     <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>登記底圖.png</t>
+  </si>
+  <si>
+    <t>測量底圖.png</t>
+  </si>
+  <si>
+    <t>地價底圖.png</t>
+  </si>
+  <si>
+    <t>地用底圖.png</t>
+  </si>
+  <si>
+    <t>檔案應用底圖.png</t>
   </si>
 </sst>
 </file>
@@ -13036,6 +13051,9 @@
       <c r="B22" s="23" t="s">
         <v>126</v>
       </c>
+      <c r="C22" t="s">
+        <v>468</v>
+      </c>
       <c r="D22" s="24" t="s">
         <v>127</v>
       </c>
@@ -13055,6 +13073,9 @@
       </c>
       <c r="B23" s="23" t="s">
         <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>468</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>132</v>
@@ -13074,6 +13095,9 @@
       <c r="B24" s="23" t="s">
         <v>135</v>
       </c>
+      <c r="C24" t="s">
+        <v>468</v>
+      </c>
       <c r="D24" s="10" t="s">
         <v>136</v>
       </c>
@@ -13092,6 +13116,9 @@
       <c r="B25" s="23" t="s">
         <v>139</v>
       </c>
+      <c r="C25" t="s">
+        <v>468</v>
+      </c>
       <c r="D25" s="10" t="s">
         <v>140</v>
       </c>
@@ -13110,6 +13137,9 @@
       <c r="B26" s="23" t="s">
         <v>143</v>
       </c>
+      <c r="C26" t="s">
+        <v>468</v>
+      </c>
       <c r="D26" s="24" t="s">
         <v>144</v>
       </c>
@@ -13130,6 +13160,9 @@
       <c r="B27" s="23" t="s">
         <v>148</v>
       </c>
+      <c r="C27" t="s">
+        <v>468</v>
+      </c>
       <c r="D27" s="26" t="s">
         <v>149</v>
       </c>
@@ -13149,6 +13182,9 @@
       </c>
       <c r="B28" s="23" t="s">
         <v>153</v>
+      </c>
+      <c r="C28" t="s">
+        <v>468</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>154</v>
@@ -13168,6 +13204,9 @@
       <c r="B29" s="23" t="s">
         <v>157</v>
       </c>
+      <c r="C29" t="s">
+        <v>468</v>
+      </c>
       <c r="D29" s="10" t="s">
         <v>158</v>
       </c>
@@ -13186,6 +13225,9 @@
       <c r="B30" s="23" t="s">
         <v>161</v>
       </c>
+      <c r="C30" t="s">
+        <v>468</v>
+      </c>
       <c r="D30" s="10" t="s">
         <v>162</v>
       </c>
@@ -13205,6 +13247,9 @@
       </c>
       <c r="B31" s="23" t="s">
         <v>166</v>
+      </c>
+      <c r="C31" t="s">
+        <v>468</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>167</v>
@@ -13224,6 +13269,9 @@
       <c r="B32" s="23" t="s">
         <v>170</v>
       </c>
+      <c r="C32" t="s">
+        <v>468</v>
+      </c>
       <c r="D32" s="10" t="s">
         <v>171</v>
       </c>
@@ -13246,6 +13294,9 @@
       <c r="B33" s="23" t="s">
         <v>176</v>
       </c>
+      <c r="C33" t="s">
+        <v>468</v>
+      </c>
       <c r="D33" s="10" t="s">
         <v>177</v>
       </c>
@@ -13267,6 +13318,9 @@
       </c>
       <c r="B34" s="23" t="s">
         <v>182</v>
+      </c>
+      <c r="C34" t="s">
+        <v>468</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>183</v>
@@ -13288,6 +13342,9 @@
       <c r="B35" s="23" t="s">
         <v>187</v>
       </c>
+      <c r="C35" t="s">
+        <v>468</v>
+      </c>
       <c r="D35" s="10" t="s">
         <v>188</v>
       </c>
@@ -13308,6 +13365,9 @@
       <c r="B36" s="23" t="s">
         <v>192</v>
       </c>
+      <c r="C36" t="s">
+        <v>468</v>
+      </c>
       <c r="D36" s="10" t="s">
         <v>193</v>
       </c>
@@ -13327,6 +13387,9 @@
       </c>
       <c r="B37" s="23" t="s">
         <v>197</v>
+      </c>
+      <c r="C37" t="s">
+        <v>468</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>198</v>
@@ -13669,6 +13732,9 @@
       <c r="B55" s="32" t="s">
         <v>9</v>
       </c>
+      <c r="C55" t="s">
+        <v>469</v>
+      </c>
       <c r="D55" s="10" t="s">
         <v>12</v>
       </c>
@@ -13689,6 +13755,9 @@
       <c r="B56" s="32" t="s">
         <v>271</v>
       </c>
+      <c r="C56" t="s">
+        <v>469</v>
+      </c>
       <c r="D56" s="10" t="s">
         <v>272</v>
       </c>
@@ -13709,6 +13778,9 @@
       <c r="B57" s="32" t="s">
         <v>276</v>
       </c>
+      <c r="C57" t="s">
+        <v>469</v>
+      </c>
       <c r="D57" s="10" t="s">
         <v>277</v>
       </c>
@@ -13728,6 +13800,9 @@
       </c>
       <c r="B58" s="32" t="s">
         <v>281</v>
+      </c>
+      <c r="C58" t="s">
+        <v>469</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>282</v>
@@ -13747,6 +13822,9 @@
       <c r="B59" s="32" t="s">
         <v>284</v>
       </c>
+      <c r="C59" t="s">
+        <v>469</v>
+      </c>
       <c r="D59" s="10" t="s">
         <v>285</v>
       </c>
@@ -13766,6 +13844,9 @@
       </c>
       <c r="B60" s="32" t="s">
         <v>289</v>
+      </c>
+      <c r="C60" t="s">
+        <v>469</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>290</v>
@@ -13785,6 +13866,9 @@
       <c r="B61" s="32" t="s">
         <v>293</v>
       </c>
+      <c r="C61" t="s">
+        <v>469</v>
+      </c>
       <c r="D61" s="10" t="s">
         <v>294</v>
       </c>
@@ -13804,6 +13888,9 @@
       </c>
       <c r="B62" s="32" t="s">
         <v>298</v>
+      </c>
+      <c r="C62" t="s">
+        <v>469</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>299</v>
@@ -13861,6 +13948,9 @@
       <c r="B65" s="35" t="s">
         <v>308</v>
       </c>
+      <c r="C65" t="s">
+        <v>470</v>
+      </c>
       <c r="D65" s="10" t="s">
         <v>309</v>
       </c>
@@ -13877,6 +13967,9 @@
       <c r="B66" s="35" t="s">
         <v>311</v>
       </c>
+      <c r="C66" t="s">
+        <v>470</v>
+      </c>
       <c r="D66" s="10" t="s">
         <v>312</v>
       </c>
@@ -13893,6 +13986,9 @@
       <c r="B67" s="35" t="s">
         <v>314</v>
       </c>
+      <c r="C67" t="s">
+        <v>470</v>
+      </c>
       <c r="D67" s="10" t="s">
         <v>315</v>
       </c>
@@ -13912,6 +14008,9 @@
       </c>
       <c r="B68" s="35" t="s">
         <v>319</v>
+      </c>
+      <c r="C68" t="s">
+        <v>470</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>320</v>
@@ -13929,6 +14028,9 @@
       <c r="B69" s="35" t="s">
         <v>322</v>
       </c>
+      <c r="C69" t="s">
+        <v>470</v>
+      </c>
       <c r="D69" s="10" t="s">
         <v>323</v>
       </c>
@@ -13945,6 +14047,9 @@
       <c r="B70" s="35" t="s">
         <v>325</v>
       </c>
+      <c r="C70" t="s">
+        <v>470</v>
+      </c>
       <c r="D70" s="10" t="s">
         <v>326</v>
       </c>
@@ -13961,6 +14066,9 @@
       <c r="B71" s="35" t="s">
         <v>328</v>
       </c>
+      <c r="C71" t="s">
+        <v>470</v>
+      </c>
       <c r="D71" s="10" t="s">
         <v>329</v>
       </c>
@@ -13976,6 +14084,9 @@
       </c>
       <c r="B72" s="35" t="s">
         <v>331</v>
+      </c>
+      <c r="C72" t="s">
+        <v>470</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>332</v>
@@ -14222,6 +14333,9 @@
       <c r="B87" s="39" t="s">
         <v>370</v>
       </c>
+      <c r="C87" t="s">
+        <v>471</v>
+      </c>
       <c r="D87" s="10" t="s">
         <v>252</v>
       </c>
@@ -14238,6 +14352,9 @@
       <c r="B88" s="39" t="s">
         <v>372</v>
       </c>
+      <c r="C88" t="s">
+        <v>471</v>
+      </c>
       <c r="D88" s="10" t="s">
         <v>373</v>
       </c>
@@ -14254,6 +14371,9 @@
       <c r="B89" s="39" t="s">
         <v>375</v>
       </c>
+      <c r="C89" t="s">
+        <v>471</v>
+      </c>
       <c r="D89" s="10" t="s">
         <v>376</v>
       </c>
@@ -14270,6 +14390,9 @@
       <c r="B90" s="39" t="s">
         <v>378</v>
       </c>
+      <c r="C90" t="s">
+        <v>471</v>
+      </c>
       <c r="D90" s="10" t="s">
         <v>379</v>
       </c>
@@ -14286,6 +14409,9 @@
       <c r="B91" s="39" t="s">
         <v>381</v>
       </c>
+      <c r="C91" t="s">
+        <v>471</v>
+      </c>
       <c r="D91" s="10" t="s">
         <v>382</v>
       </c>
@@ -14302,6 +14428,9 @@
       <c r="B92" s="39" t="s">
         <v>384</v>
       </c>
+      <c r="C92" t="s">
+        <v>471</v>
+      </c>
       <c r="D92" s="10" t="s">
         <v>385</v>
       </c>
@@ -14317,6 +14446,9 @@
       </c>
       <c r="B93" s="39" t="s">
         <v>387</v>
+      </c>
+      <c r="C93" t="s">
+        <v>471</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>388</v>
@@ -14563,6 +14695,9 @@
       <c r="B108" s="41" t="s">
         <v>427</v>
       </c>
+      <c r="C108" t="s">
+        <v>472</v>
+      </c>
       <c r="D108" s="10" t="s">
         <v>245</v>
       </c>
@@ -14579,6 +14714,9 @@
       <c r="B109" s="41" t="s">
         <v>429</v>
       </c>
+      <c r="C109" t="s">
+        <v>472</v>
+      </c>
       <c r="D109" s="10" t="s">
         <v>430</v>
       </c>
@@ -14595,6 +14733,9 @@
       <c r="B110" s="41" t="s">
         <v>432</v>
       </c>
+      <c r="C110" t="s">
+        <v>472</v>
+      </c>
       <c r="D110" s="10" t="s">
         <v>433</v>
       </c>
@@ -14606,6 +14747,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A94:H94"/>
     <mergeCell ref="A106:H106"/>
     <mergeCell ref="A53:H53"/>
@@ -14613,11 +14759,6 @@
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LINE_Bot_內容對照表.xlsx
+++ b/LINE_Bot_內容對照表.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF35EAF-C88B-44D2-AB4C-385B81133ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93295951-C1A6-48FF-883F-ADB4EC8547D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="說明" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="509">
   <si>
     <t>欄位說明</t>
   </si>
@@ -201,24 +201,15 @@
     <t>【連結】新湖地政所官方網站</t>
   </si>
   <si>
-    <t>https://sinhu.land.hsinchu.gov.tw/</t>
-  </si>
-  <si>
     <t>RM-2</t>
   </si>
   <si>
-    <t>查詢案件辦理情形</t>
-  </si>
-  <si>
     <t>查詢案件</t>
   </si>
   <si>
     <t>【連結】案件查詢系統</t>
   </si>
   <si>
-    <t>https://land.hsinchu.gov.tw/valueprice/?mode=queryCasedo_show&amp;parent_id=10309&amp;type_id=10309</t>
-  </si>
-  <si>
     <t>RM-3</t>
   </si>
   <si>
@@ -228,9 +219,6 @@
     <t>【連結】線上取號系統</t>
   </si>
   <si>
-    <t>https://sinhu.land.hsinchu.gov.tw/jhubei_waitNum/?mode=add&amp;parent_id=10475&amp;type_id=10475</t>
-  </si>
-  <si>
     <t>RM-4</t>
   </si>
   <si>
@@ -252,9 +240,6 @@
     <t>【連結】預約服務系統</t>
   </si>
   <si>
-    <t>https://sinhu.land.hsinchu.gov.tw/content/?parent_id=10338&amp;type_id=10338</t>
-  </si>
-  <si>
     <t>RM-6</t>
   </si>
   <si>
@@ -277,17 +262,6 @@
   </si>
   <si>
     <t>（非關鍵字觸發）</t>
-  </si>
-  <si>
-    <t>阿吸，您好！
-有任何地政相關的問題歡迎(pencil)輸入以下數字取得更多相關資訊，或撥打本所電話03-5903588，將有人員進一步協助您！
-【 1 】－(sunny)上班時間
-【 2 】－(telephone)聯絡電話
-【 3 】－(school)地所住址
-【 4 】－(monitor)官方網站
-【 5 】－(smartphone)粉絲專頁
-【 6 】－ 💌其他問題
-快邀請親朋好友一起加入官方LINE，將會不定時收到最新活動消息唷！(two hearts)</t>
   </si>
   <si>
     <t>非關鍵字時自動觸發
@@ -8112,37 +8086,6 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>QR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>更正編定申請書</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>.jpg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="細明體"/>
         <family val="3"/>
         <charset val="136"/>
@@ -11003,11 +10946,6 @@
     <t>實價登錄</t>
   </si>
   <si>
-    <t>請輸入代號取得更多資訊：
-【301】申報種類
-【302】買賣申報...</t>
-  </si>
-  <si>
     <t>觸發 PRICE-阿吸</t>
   </si>
   <si>
@@ -11222,11 +11160,6 @@
   </si>
   <si>
     <t>地用</t>
-  </si>
-  <si>
-    <t>請輸入代號取得更多地用資訊：
-【11】分辨非都市土地和都市土地
-【12】非都市土地種類...</t>
   </si>
   <si>
     <t>觸發 LAND-xx</t>
@@ -11647,13 +11580,4934 @@
   </si>
   <si>
     <t>檔案應用底圖.png</t>
+  </si>
+  <si>
+    <t>https://sinhu.land.hsinchu.gov.tw/</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://land.hsinchu.gov.tw/valueprice/?mode=queryCasedo_show&amp;parent_id=10309&amp;type_id=10309</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>查詢案件辦理情形</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>線上取號</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sinhu.land.hsinchu.gov.tw/jhubei_waitNum/?mode=add&amp;parent_id=10475&amp;type_id=10475</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>臉書粉專</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sinhu.land.hsinchu.gov.tw/content/?parent_id=10338&amp;type_id=10338</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>邀請好友</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>官方網站</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <t>預約服務</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！
+有任何地政相關的問題歡迎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(pencil)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>輸入以下數字取得更多相關資訊，或撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>03-5903588</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有人員進一步協助您！
+【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(sunny)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>上班時間
+【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(telephone)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>聯絡電話
+【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(school)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>地所住址
+【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(monitor)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>官方網站
+【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(smartphone)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>粉絲專頁
+【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】－</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>其他問題
+快邀請親朋好友一起加入官方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將會不定時收到最新活動消息唷！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(two hearts)</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>若您欲查詢公告土地現值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>可至桃園市政府地政局網站，輸入欲查詢之地段地號進行查詢：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.land.tycg.gov.tw/chaspx/SQry1.aspx/517
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>304</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>309</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>若您欲試算土地移轉需繳納之增值稅金額，可至桃園市政府地政局網站進行試算查詢：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.land.tycg.gov.tw/chaspx/SQry1.aspx/517
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>該網站僅提供試算功能，實際稅額仍應以稅務機關核定為準，若尚有相關稅賦問題請逕洽桃園市政府地方稅務局中壢分局，電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4515111</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+(pencil)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>請輸入以下數字取得更多實價登錄相關資訊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">~
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>301</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】實價登錄申報種類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>302</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】買賣實價登錄申報</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>303</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】租賃及預售屋實價登錄申報</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>304</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】實價登錄申報期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>305</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】實價登錄申報義務人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>306</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】實價登錄查詢網站</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>買賣成交資訊實價登錄可分為「線上登錄，紙本送件」及「紙本申報」兩種方式，申報完成後均應於申請買賣移轉登記時一併送件。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「線上登錄，紙本送件」可至內政部不動產成交資訊及預售屋資訊申報網</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">https://vlir.land.moi.gov.tw/  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>辦理。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>306</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>需申報實價登錄的種類如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>買賣不動產並辦理登記時。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>透過建商或不動產經紀業者成交之預售屋。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>由不動產經紀業或租賃住宅包租業居間成交之租賃。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>預售屋解約。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>買賣案件應於申請買賣移轉登記時一併辦理，租賃及預售屋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>成交、解約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>案件則應於立契之日起</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>內完成申報。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>若欲查詢實價登錄資訊，可至以下網站進行查詢：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>內政部不動產交易實價查詢服務網</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> https://lvr.land.moi.gov.tw/
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園住宅及不動產資訊桃寶網</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> https://taobao.tycg.gov.tw/Home
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市不動產交易</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>指通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> https://e91plus.tycg.gov.tw/Index</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>租賃及預售屋實價登錄案件可分為「憑證登錄，線上申報」、「線上登錄，紙本送件」及「紙本申報」三種方式，提醒您若採「線上登錄，紙本送件」及「紙本申報」兩種方式申報，需於申報期限內將紙本資料送至地政事務所收件，才能完成申報手續。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>各類實價登錄申報義務人分別如下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">:
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>買賣案件：買賣雙方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>租賃案件：不動產經紀業及租賃住宅包租業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>預售屋銷售案件：銷售預售屋者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建商</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>或不動產經紀業者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>預售屋解約案件：銷售預售屋者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建商或自然人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>地籍謄本櫃員機提供之服務如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>設置地點：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園地政事務所、平鎮地政事務所、龜山地政事務所、市府地政便民工作站與本所六和地政便民工作站。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>服務項目：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>目前可以申請桃園市、台北市、新北市、台中市、嘉義市第一、二類土地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>建物登記謄本、地籍圖及建物測量成果圖謄本申請。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>繳費方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使用悠遊卡、一卡通或信用卡感應付款，目前不接受現金。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>身分驗證方式：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+(1) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>持身分證明文件至本市各地政事務所臨櫃辦理。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+(2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>使用桃園市地政</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>管家網頁版進行線上申請</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>申請人須於本市各地政事務所曾經申請登記、測量、謄本案件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。網址：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">https://www.land.tycg.gov.tw:18018/taoyuan_app2025/index.html
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>507</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>土地基本資料申請方式分為「臨櫃申請」和「網路申請」：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>臨櫃申請</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:
+(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>申請之土地需為該地政事務所管轄才可受理。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+(2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>填寫「土地基本資料庫電子資料流通申請表」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>份。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+(3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攜帶申請人身份證明文件及印章。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>網路申請</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:
+(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>需具備「自然人憑證」或「工商憑證」。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+(2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>至「桃園網路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>指通」，點選「地政資訊」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>「土地基本資料庫電子資料流通申請」項目，依照畫面步驟操作即可完成申請。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>507</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>土地基本資料依「桃園市土地基本資料庫電子資料收費標準」計費，連結如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://law.tycg.gov.tw/LawContent.aspx?id=GL000252 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>507</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>辦理更正編定，可向土地所在地政事務所申請，除門牌編釘證明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>佐證資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>及航照圖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>佐證資料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>外，請檢具檢具以下其一文件：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>曾於該建物設籍之戶籍謄本、繳納房屋稅籍證明、用電證明或繳納自來水費用證明、建物完工證明書或其他證明文件。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>本所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>LINE+ibon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>卡厲害服務</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">~ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>為您搜尋到的文件如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【更正編定申請書】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　列印代碼如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（提醒您，至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ibon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>機台輸入以下列印代碼或掃描下方圖片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>QRcode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，即可列印文件）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+        ASUSJ5VXFSVGH
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　電子檔下載點：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.asuswebstorage.com/navigate/a/#/s/94EEE13CF36646168905E84DC1E90F1B6
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【更正編定申請書填寫範例】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　電子檔下載點：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.asuswebstorage.com/navigate/a/#/s/C0E5EAEA43574243AFAA2994D367E0656
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>414</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>419</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>QR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>更正編定申請書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>.jpg</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>更正編定申請書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.jpg</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>辦理變更編定，請檢具下列資料向土地所在地縣市政府地政局申請：變更編定申請書、興辦事業計畫核准文件、變更編定同意書、土地登記簿謄本及地籍圖謄本、土地使用計畫配置圖及位置圖。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>欲查詢土地參考資訊檔資料，可向地政事務所申請或向內政部「土地建物參考資訊檔」官網免費查詢：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://moiref.moi.gov.tw/pubref/</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>內政部國土管理署建置「各直轄市、縣市國土功能分區圖草案公開展覽資訊查詢系統」供查詢！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>網址：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://up.tcd.gov.tw/Ex3S/ExWeb.aspx</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>農地不可以違規使用，必須申請容許使用、臨時使用或變更土地使用地類別後再行使用，未經申請違規者，將依區域計畫法處</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>萬罰鍰。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>欲查詢土地容許使用資訊，可洽土地所在地縣市政府地政局查詢可供容許使用的項目，或請點選法規資料庫查詢</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://law.moj.gov.tw/LawClass/LawSingle.aspx?pcode=D0060013&amp;flno=6</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>輸入下列數字</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>可獲得更多地用資訊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(sunny)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】分辨非都市土地和都市土地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】非都市土地種類</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】更正編定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】地目變更</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】查詢地目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】變更編定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】土地參考資訊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】容許使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】土地違規使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】國土計畫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>】建管時間</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>土地謄本載有使用分區及使用地類別之土地即為非都市土地，反之即為都市土地。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>非都市土地依其使用分區之性質，編定為甲種建築、乙種建築、丙種建築、丁種建築、農牧、林業、養殖、鹽業、礦業、窯業、交通、水利、遊憩、古蹟保存、生態保護、國土保安、殯葬、海域、特定目的事業等使用地。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>LINE+ibon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>卡厲害服務</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">~ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>為您搜尋到的文件如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【更正編定申請書】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　列印代碼如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（提醒您，至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ibon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>機台輸入以下列印代碼或掃描下方圖片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>QRcode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，即可列印文件）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+        ASUSJ5VXFSVGH
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　電子檔下載點：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.asuswebstorage.com/navigate/a/#/s/94EEE13CF36646168905E84DC1E90F1B6
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【更正編定申請書填寫範例】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　電子檔下載點：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.asuswebstorage.com/navigate/a/#/s/C0E5EAEA43574243AFAA2994D367E0656
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>如您尚有其他問題，可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>414</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>419</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+106</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年起地目等則制度已廢除，無法辦理地目變更相關業務。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>地目等則已經廢除，土地謄本上不再顯示土地使用分區及使用地類別相關資料，如需查詢地目等則資料可向地政事務所申請人工登記簿謄本或地籍整理清冊。</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>田地目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1-12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>等則為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>62</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>田地目</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>13-26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>等則為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>中壢區</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>為內政部指定日期為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>62</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>桃園市公告編定為</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有關檔案應用申請相關說明，可參閱本所官網檔案應用專區</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Q&amp;A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資訊，連結如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.zhongli-land.tycg.gov.tw/archive_QA.htm</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>本所</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>LINE+ibon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>卡厲害</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">~ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>為您搜尋到的文件如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【檔案應用申請書】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　列印代碼如下：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>（提醒您，至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>ibon</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>機台輸入以下列印代碼或掃描下方圖片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>QRcode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，即可列印文件）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+      ASUSXSVFN5A4N
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>　電子檔下載點：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+https://www.asuswebstorage.com/navigate/a/#/s/9578C16467DC4329B9BF12B95B74768F6</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>檔案應用申請書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.jpg</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>檔案應用代理人委任書</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>.jpg</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>有關本所志工招募詳細資訊可至本所官網</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>便民服務</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>志工園地查詢，或撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>412</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">418 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>網址：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://www.zhongli-land.tycg.gov.tw/cl.aspx?n=5563</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>阿吸，您好！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>本所每年寒暑假招募青年志工的資訊會在假期前兩星期於本所官網最新消息公布。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>報名應備資料有：報名表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>張、輪值時段需求表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>張、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>吋大頭照</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>張、在學證明</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>學生證或註冊單</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>影本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>份；如您有其他問題可撥打本所電話</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>03-4917647</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>分機</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>412</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>418</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，將有專人進一步協助您，謝謝您！</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11822,6 +16676,20 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -11920,10 +16788,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -11958,9 +16827,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12079,9 +16945,28 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -12670,14 +17555,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="36" customHeight="1">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="7" t="s">
         <v>53</v>
       </c>
@@ -12686,8 +17571,8 @@
       <c r="A3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>55</v>
+      <c r="B3" s="55" t="s">
+        <v>472</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>55</v>
@@ -12698,2060 +17583,2143 @@
       <c r="F3" s="9"/>
       <c r="G3" s="11"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="9" t="s">
-        <v>57</v>
+      <c r="I3" s="54" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="36" customHeight="1">
       <c r="A4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>61</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="11"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="9" t="s">
-        <v>62</v>
+      <c r="I4" s="54" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="36" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>64</v>
+        <v>60</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>467</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F5" s="9"/>
       <c r="G5" s="11"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
-        <v>66</v>
+      <c r="I5" s="54" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="36" customHeight="1">
       <c r="A6" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>469</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="11"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="36" customHeight="1">
       <c r="A7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>72</v>
+        <v>67</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>473</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="11"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="9" t="s">
-        <v>74</v>
+      <c r="I7" s="54" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>471</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="11"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1">
-      <c r="A9" s="52"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
       <c r="I9" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="184.5" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>474</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="11"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="15" t="s">
-        <v>84</v>
+      <c r="I10" s="14" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="84" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D11" s="10"/>
-      <c r="E11" s="16" t="s">
-        <v>87</v>
+      <c r="E11" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="11"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="118.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>460</v>
+        <v>84</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>451</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="15" t="s">
-        <v>92</v>
+      <c r="I12" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1">
-      <c r="A13" s="52"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
       <c r="I13" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="36" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>97</v>
+        <v>90</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>91</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="11"/>
       <c r="H14" s="13"/>
-      <c r="I14" s="20" t="s">
-        <v>98</v>
+      <c r="I14" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="54.75" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>102</v>
+        <v>95</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="11"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="20" t="s">
-        <v>98</v>
+      <c r="I15" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="36" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>106</v>
+        <v>99</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="11"/>
       <c r="H16" s="13"/>
-      <c r="I16" s="20" t="s">
-        <v>98</v>
+      <c r="I16" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="36" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>55</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>109</v>
+        <v>102</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="11"/>
       <c r="H17" s="13"/>
-      <c r="I17" s="20" t="s">
-        <v>98</v>
+      <c r="I17" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="36" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>113</v>
+        <v>106</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="11"/>
       <c r="H18" s="13"/>
-      <c r="I18" s="20" t="s">
-        <v>98</v>
+      <c r="I18" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="36" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>117</v>
+        <v>110</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>111</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="11"/>
       <c r="H19" s="13"/>
-      <c r="I19" s="20" t="s">
-        <v>98</v>
+      <c r="I19" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="36" customHeight="1">
-      <c r="A20" s="52"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="36" customHeight="1">
-      <c r="A21" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>120</v>
+      <c r="A21" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" s="23"/>
-      <c r="I21" s="23" t="s">
-        <v>124</v>
+        <v>115</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="36" customHeight="1">
-      <c r="A22" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>126</v>
+      <c r="A22" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>468</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>129</v>
+        <v>459</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>123</v>
       </c>
       <c r="G22" s="11"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" spans="1:9" ht="36" customHeight="1">
-      <c r="A23" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>131</v>
+      <c r="A23" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="23"/>
+        <v>126</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="22"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" spans="1:9" ht="36" customHeight="1">
-      <c r="A24" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>135</v>
+      <c r="A24" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="F24" s="23"/>
+        <v>130</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" s="22"/>
       <c r="G24" s="11"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" spans="1:9" ht="36" customHeight="1">
-      <c r="A25" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>139</v>
+      <c r="A25" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="F25" s="23"/>
+        <v>134</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="22"/>
       <c r="G25" s="11"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" spans="1:9" ht="36" customHeight="1">
-      <c r="A26" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>143</v>
+      <c r="A26" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>468</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>146</v>
+        <v>459</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>140</v>
       </c>
       <c r="G26" s="11"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" ht="36" customHeight="1">
-      <c r="A27" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>148</v>
+      <c r="A27" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>468</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>151</v>
+        <v>459</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>145</v>
       </c>
       <c r="G27" s="11"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" spans="1:9" ht="36" customHeight="1">
-      <c r="A28" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>153</v>
+      <c r="A28" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="F28" s="23"/>
+        <v>148</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" s="22"/>
       <c r="G28" s="11"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" spans="1:9" ht="36" customHeight="1">
-      <c r="A29" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>157</v>
+      <c r="A29" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="23"/>
+        <v>152</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="22"/>
       <c r="G29" s="11"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" spans="1:9" ht="36" customHeight="1">
-      <c r="A30" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="B30" s="23" t="s">
-        <v>161</v>
+      <c r="A30" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F30" s="23"/>
+        <v>156</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" s="22"/>
       <c r="G30" s="11"/>
-      <c r="H30" s="23"/>
-      <c r="I30" s="23" t="s">
-        <v>164</v>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="36" customHeight="1">
-      <c r="A31" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>166</v>
+      <c r="A31" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="F31" s="23"/>
+        <v>161</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="F31" s="22"/>
       <c r="G31" s="11"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="23"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" spans="1:9" ht="36" customHeight="1">
-      <c r="A32" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>170</v>
+      <c r="A32" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="F32" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="23"/>
+        <v>165</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="36" customHeight="1">
-      <c r="A33" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>176</v>
+      <c r="A33" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="F33" s="25" t="s">
-        <v>179</v>
+        <v>171</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="G33" s="11"/>
-      <c r="H33" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="I33" s="23"/>
+      <c r="H33" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="36" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>182</v>
+      <c r="A34" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>176</v>
       </c>
       <c r="C34" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>185</v>
+        <v>177</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>179</v>
       </c>
       <c r="G34" s="11"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="23"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
     </row>
     <row r="35" spans="1:9" ht="36" customHeight="1">
-      <c r="A35" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>187</v>
+      <c r="A35" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>181</v>
       </c>
       <c r="C35" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>190</v>
+        <v>182</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>184</v>
       </c>
       <c r="G35" s="11"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
     </row>
     <row r="36" spans="1:9" ht="36" customHeight="1">
-      <c r="A36" s="22" t="s">
-        <v>191</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>192</v>
+      <c r="A36" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>186</v>
       </c>
       <c r="C36" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>195</v>
+        <v>187</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>189</v>
       </c>
       <c r="G36" s="11"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
     </row>
     <row r="37" spans="1:9" ht="36" customHeight="1">
-      <c r="A37" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>197</v>
+      <c r="A37" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>191</v>
       </c>
       <c r="C37" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="F37" s="23"/>
+        <v>192</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F37" s="22"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
     </row>
     <row r="38" spans="1:9" ht="36" customHeight="1">
-      <c r="A38" s="52"/>
-      <c r="B38" s="53"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="53"/>
+      <c r="A38" s="51"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
       <c r="I38" s="7" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="36" customHeight="1">
-      <c r="A39" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>202</v>
+      <c r="A39" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>196</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="E39" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="F39" s="23"/>
+        <v>197</v>
+      </c>
+      <c r="E39" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39" s="22"/>
       <c r="G39" s="11"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23" t="s">
-        <v>205</v>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="36" customHeight="1">
-      <c r="A40" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>207</v>
+      <c r="A40" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>201</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="F40" s="23"/>
+        <v>202</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" s="22"/>
       <c r="G40" s="11"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="23" t="s">
-        <v>210</v>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="36" customHeight="1">
-      <c r="A41" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>212</v>
+      <c r="A41" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>206</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="F41" s="23"/>
+        <v>207</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="22"/>
       <c r="G41" s="11"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="23"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
     </row>
     <row r="42" spans="1:9" ht="36" customHeight="1">
-      <c r="A42" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="B42" s="23" t="s">
-        <v>216</v>
+      <c r="A42" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>210</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="F42" s="23"/>
+        <v>211</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" s="22"/>
       <c r="G42" s="11"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
     </row>
     <row r="43" spans="1:9" ht="36" customHeight="1">
-      <c r="A43" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>220</v>
+      <c r="A43" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>214</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="E43" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="F43" s="23"/>
-      <c r="G43" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="H43" s="23"/>
-      <c r="I43" s="23"/>
+        <v>215</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" s="22"/>
+      <c r="G43" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
     </row>
     <row r="44" spans="1:9" ht="36" customHeight="1">
-      <c r="A44" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>225</v>
+      <c r="A44" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>219</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="E44" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="F44" s="23"/>
+        <v>220</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44" s="22"/>
       <c r="G44" s="11"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
     </row>
     <row r="45" spans="1:9" ht="36" customHeight="1">
-      <c r="A45" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>229</v>
+      <c r="A45" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>223</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="F45" s="23"/>
+        <v>224</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="F45" s="22"/>
       <c r="G45" s="11"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="23"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
     </row>
     <row r="46" spans="1:9" ht="36" customHeight="1">
-      <c r="A46" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>233</v>
+      <c r="A46" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>227</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="F46" s="23"/>
+        <v>228</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="F46" s="22"/>
       <c r="G46" s="11"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
     </row>
     <row r="47" spans="1:9" ht="36" customHeight="1">
-      <c r="A47" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="B47" s="23" t="s">
-        <v>237</v>
+      <c r="A47" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>231</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="E47" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="F47" s="23"/>
+        <v>232</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>233</v>
+      </c>
+      <c r="F47" s="22"/>
       <c r="G47" s="11"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
     </row>
     <row r="48" spans="1:9" ht="36" customHeight="1">
-      <c r="A48" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>177</v>
+      <c r="A48" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>171</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="F48" s="25" t="s">
-        <v>179</v>
+        <v>235</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="G48" s="11"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
     </row>
     <row r="49" spans="1:9" ht="36" customHeight="1">
-      <c r="A49" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="B49" s="23" t="s">
-        <v>183</v>
+      <c r="A49" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>177</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="F49" s="25" t="s">
-        <v>185</v>
+        <v>237</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>179</v>
       </c>
       <c r="G49" s="11"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
     </row>
     <row r="50" spans="1:9" ht="36" customHeight="1">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="G50" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="H50" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="B50" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="F50" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="G50" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>250</v>
-      </c>
-      <c r="I50" s="23"/>
+      <c r="I50" s="22"/>
     </row>
     <row r="51" spans="1:9" ht="36" customHeight="1">
-      <c r="A51" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>252</v>
+      <c r="A51" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>246</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>254</v>
-      </c>
-      <c r="F51" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="G51" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
+        <v>247</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="G51" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
     </row>
     <row r="52" spans="1:9" ht="36" customHeight="1">
-      <c r="A52" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>258</v>
+      <c r="A52" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>251</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="F52" s="30" t="s">
-        <v>261</v>
+        <v>252</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="F52" s="29" t="s">
+        <v>254</v>
       </c>
       <c r="G52" s="11"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:9" ht="36" customHeight="1">
-      <c r="A53" s="52"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="53"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="53"/>
-      <c r="H53" s="53"/>
+      <c r="A53" s="51"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
       <c r="I53" s="7" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="36" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="B54" s="32" t="s">
-        <v>264</v>
+      <c r="A54" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>257</v>
       </c>
       <c r="C54" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="E54" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="F54" s="32"/>
+        <v>258</v>
+      </c>
+      <c r="E54" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="F54" s="31"/>
       <c r="G54" s="11"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32" t="s">
-        <v>124</v>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="36" customHeight="1">
-      <c r="A55" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="B55" s="32" t="s">
+      <c r="A55" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="B55" s="31" t="s">
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="F55" s="33" t="s">
-        <v>269</v>
+      <c r="E55" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>262</v>
       </c>
       <c r="G55" s="11"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
     </row>
     <row r="56" spans="1:9" ht="36" customHeight="1">
-      <c r="A56" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="B56" s="32" t="s">
-        <v>271</v>
+      <c r="A56" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>264</v>
       </c>
       <c r="C56" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>274</v>
+        <v>265</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>267</v>
       </c>
       <c r="G56" s="11"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
     </row>
     <row r="57" spans="1:9" ht="36" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="B57" s="32" t="s">
-        <v>276</v>
+      <c r="A57" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>269</v>
       </c>
       <c r="C57" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="F57" s="32"/>
-      <c r="G57" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
+        <v>270</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="F57" s="31"/>
+      <c r="G57" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
     </row>
     <row r="58" spans="1:9" ht="36" customHeight="1">
-      <c r="A58" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="B58" s="32" t="s">
-        <v>281</v>
+      <c r="A58" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="F58" s="32"/>
+        <v>275</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F58" s="31"/>
       <c r="G58" s="11"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
     </row>
     <row r="59" spans="1:9" ht="36" customHeight="1">
-      <c r="A59" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="B59" s="32" t="s">
-        <v>284</v>
+      <c r="A59" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>277</v>
       </c>
       <c r="C59" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>287</v>
+        <v>278</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="F59" s="32" t="s">
+        <v>280</v>
       </c>
       <c r="G59" s="11"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="31"/>
     </row>
     <row r="60" spans="1:9" ht="36" customHeight="1">
-      <c r="A60" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="B60" s="32" t="s">
-        <v>289</v>
+      <c r="A60" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="F60" s="32"/>
+        <v>283</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="F60" s="31"/>
       <c r="G60" s="11"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
     </row>
     <row r="61" spans="1:9" ht="36" customHeight="1">
-      <c r="A61" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="B61" s="32" t="s">
-        <v>293</v>
+      <c r="A61" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>286</v>
       </c>
       <c r="C61" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="F61" s="33" t="s">
-        <v>296</v>
+        <v>287</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="F61" s="32" t="s">
+        <v>289</v>
       </c>
       <c r="G61" s="11"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
     </row>
     <row r="62" spans="1:9" ht="36" customHeight="1">
-      <c r="A62" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="B62" s="32" t="s">
-        <v>298</v>
+      <c r="A62" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>291</v>
       </c>
       <c r="C62" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="F62" s="33" t="s">
-        <v>301</v>
+        <v>292</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>294</v>
       </c>
       <c r="G62" s="11"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
+      <c r="H62" s="31"/>
+      <c r="I62" s="31"/>
     </row>
     <row r="63" spans="1:9" ht="36" customHeight="1">
-      <c r="A63" s="52"/>
-      <c r="B63" s="53"/>
-      <c r="C63" s="54"/>
-      <c r="D63" s="53"/>
-      <c r="E63" s="53"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="53"/>
+      <c r="A63" s="51"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="52"/>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
       <c r="I63" s="7" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="36" customHeight="1">
-      <c r="A64" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="B64" s="35" t="s">
-        <v>304</v>
+      <c r="A64" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>297</v>
       </c>
       <c r="C64" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>305</v>
-      </c>
-      <c r="E64" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="F64" s="35"/>
+        <v>298</v>
+      </c>
+      <c r="E64" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="F64" s="34"/>
       <c r="G64" s="11"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35" t="s">
-        <v>124</v>
+      <c r="H64" s="34"/>
+      <c r="I64" s="34" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="36" customHeight="1">
-      <c r="A65" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="B65" s="35" t="s">
-        <v>308</v>
+      <c r="A65" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>301</v>
       </c>
       <c r="C65" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="E65" s="11"/>
-      <c r="F65" s="35"/>
+        <v>302</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="F65" s="34"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
     </row>
     <row r="66" spans="1:9" ht="36" customHeight="1">
-      <c r="A66" s="34" t="s">
-        <v>310</v>
-      </c>
-      <c r="B66" s="35" t="s">
-        <v>311</v>
+      <c r="A66" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>304</v>
       </c>
       <c r="C66" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="E66" s="11"/>
-      <c r="F66" s="35"/>
+        <v>305</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>476</v>
+      </c>
+      <c r="F66" s="34"/>
       <c r="G66" s="11"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
     </row>
     <row r="67" spans="1:9" ht="36" customHeight="1">
-      <c r="A67" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="B67" s="35" t="s">
-        <v>314</v>
+      <c r="A67" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="E67" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="F67" s="35"/>
-      <c r="G67" s="11"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35" t="s">
-        <v>317</v>
+        <v>308</v>
+      </c>
+      <c r="E67" s="56" t="s">
+        <v>477</v>
+      </c>
+      <c r="F67" s="34"/>
+      <c r="G67" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="36" customHeight="1">
-      <c r="A68" s="34" t="s">
-        <v>318</v>
-      </c>
-      <c r="B68" s="35" t="s">
-        <v>319</v>
+      <c r="A68" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>311</v>
       </c>
       <c r="C68" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="E68" s="11"/>
-      <c r="F68" s="35"/>
+        <v>312</v>
+      </c>
+      <c r="E68" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="F68" s="34"/>
       <c r="G68" s="11"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
     </row>
     <row r="69" spans="1:9" ht="36" customHeight="1">
-      <c r="A69" s="34" t="s">
-        <v>321</v>
-      </c>
-      <c r="B69" s="35" t="s">
-        <v>322</v>
+      <c r="A69" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>314</v>
       </c>
       <c r="C69" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="E69" s="11"/>
-      <c r="F69" s="35"/>
+        <v>315</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="F69" s="34"/>
       <c r="G69" s="11"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
     </row>
     <row r="70" spans="1:9" ht="36" customHeight="1">
-      <c r="A70" s="34" t="s">
-        <v>324</v>
-      </c>
-      <c r="B70" s="35" t="s">
-        <v>325</v>
+      <c r="A70" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>317</v>
       </c>
       <c r="C70" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="E70" s="11"/>
-      <c r="F70" s="35"/>
+        <v>318</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>481</v>
+      </c>
+      <c r="F70" s="34"/>
       <c r="G70" s="11"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
+      <c r="H70" s="34"/>
+      <c r="I70" s="34"/>
     </row>
     <row r="71" spans="1:9" ht="36" customHeight="1">
-      <c r="A71" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="B71" s="35" t="s">
-        <v>328</v>
+      <c r="A71" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>320</v>
       </c>
       <c r="C71" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="E71" s="11"/>
-      <c r="F71" s="35"/>
+        <v>321</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="F71" s="34"/>
       <c r="G71" s="11"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
     </row>
     <row r="72" spans="1:9" ht="36" customHeight="1">
-      <c r="A72" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="B72" s="35" t="s">
-        <v>331</v>
+      <c r="A72" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>323</v>
       </c>
       <c r="C72" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="E72" s="11"/>
-      <c r="F72" s="35"/>
+        <v>324</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="F72" s="34"/>
       <c r="G72" s="11"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
     </row>
     <row r="73" spans="1:9" ht="36" customHeight="1">
-      <c r="A73" s="52"/>
-      <c r="B73" s="53"/>
-      <c r="C73" s="54"/>
-      <c r="D73" s="53"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="53"/>
-      <c r="G73" s="53"/>
-      <c r="H73" s="53"/>
+      <c r="A73" s="51"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="52"/>
+      <c r="E73" s="52"/>
+      <c r="F73" s="52"/>
+      <c r="G73" s="52"/>
+      <c r="H73" s="52"/>
       <c r="I73" s="7" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="36" customHeight="1">
-      <c r="A74" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="B74" s="35" t="s">
-        <v>332</v>
+      <c r="A74" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B74" s="34" t="s">
+        <v>324</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="E74" s="11"/>
-      <c r="F74" s="35"/>
+        <v>327</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="F74" s="34"/>
       <c r="G74" s="11"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="H74" s="34"/>
+      <c r="I74" s="34"/>
     </row>
     <row r="75" spans="1:9" ht="36" customHeight="1">
-      <c r="A75" s="34" t="s">
-        <v>336</v>
-      </c>
-      <c r="B75" s="35" t="s">
-        <v>337</v>
+      <c r="A75" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>329</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="E75" s="11"/>
-      <c r="F75" s="35"/>
+        <v>330</v>
+      </c>
+      <c r="E75" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="F75" s="34"/>
       <c r="G75" s="11"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
     </row>
     <row r="76" spans="1:9" ht="36" customHeight="1">
-      <c r="A76" s="34" t="s">
-        <v>339</v>
-      </c>
-      <c r="B76" s="35" t="s">
-        <v>340</v>
+      <c r="A76" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>332</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="E76" s="11"/>
-      <c r="F76" s="35"/>
+        <v>333</v>
+      </c>
+      <c r="E76" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="F76" s="34"/>
       <c r="G76" s="11"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="34"/>
     </row>
     <row r="77" spans="1:9" ht="36" customHeight="1">
-      <c r="A77" s="34" t="s">
-        <v>342</v>
-      </c>
-      <c r="B77" s="35" t="s">
-        <v>343</v>
+      <c r="A77" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>335</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="E77" s="11"/>
-      <c r="F77" s="35"/>
+        <v>336</v>
+      </c>
+      <c r="E77" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="F77" s="34"/>
       <c r="G77" s="11"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="34"/>
     </row>
     <row r="78" spans="1:9" ht="36" customHeight="1">
-      <c r="A78" s="34" t="s">
-        <v>345</v>
-      </c>
-      <c r="B78" s="35" t="s">
-        <v>346</v>
+      <c r="A78" s="33" t="s">
+        <v>337</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>338</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="E78" s="11"/>
-      <c r="F78" s="35"/>
+        <v>339</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="F78" s="34"/>
       <c r="G78" s="11"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
     </row>
     <row r="79" spans="1:9" ht="36" customHeight="1">
-      <c r="A79" s="34" t="s">
-        <v>348</v>
-      </c>
-      <c r="B79" s="35" t="s">
-        <v>326</v>
+      <c r="A79" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>318</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="E79" s="11"/>
-      <c r="F79" s="35"/>
+        <v>341</v>
+      </c>
+      <c r="E79" s="26" t="s">
+        <v>481</v>
+      </c>
+      <c r="F79" s="34"/>
       <c r="G79" s="11"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
+      <c r="H79" s="34"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:9" ht="36" customHeight="1">
-      <c r="A80" s="52"/>
-      <c r="B80" s="53"/>
-      <c r="C80" s="54"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="53"/>
-      <c r="H80" s="53"/>
+      <c r="A80" s="51"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="52"/>
+      <c r="E80" s="52"/>
+      <c r="F80" s="52"/>
+      <c r="G80" s="52"/>
+      <c r="H80" s="52"/>
       <c r="I80" s="7" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="36" customHeight="1">
-      <c r="A81" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="B81" s="37" t="s">
-        <v>352</v>
+      <c r="A81" s="35" t="s">
+        <v>343</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>344</v>
       </c>
       <c r="C81" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="E81" s="37" t="s">
-        <v>354</v>
-      </c>
-      <c r="F81" s="37"/>
+        <v>345</v>
+      </c>
+      <c r="E81" s="36" t="s">
+        <v>346</v>
+      </c>
+      <c r="F81" s="36"/>
       <c r="G81" s="11"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="37" t="s">
-        <v>124</v>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="36" customHeight="1">
-      <c r="A82" s="36" t="s">
-        <v>355</v>
-      </c>
-      <c r="B82" s="37" t="s">
-        <v>356</v>
+      <c r="A82" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>348</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="E82" s="11"/>
-      <c r="F82" s="37"/>
+        <v>349</v>
+      </c>
+      <c r="E82" s="26" t="s">
+        <v>484</v>
+      </c>
+      <c r="F82" s="36"/>
       <c r="G82" s="11"/>
-      <c r="H82" s="37"/>
-      <c r="I82" s="37"/>
+      <c r="H82" s="36"/>
+      <c r="I82" s="36"/>
     </row>
     <row r="83" spans="1:9" ht="36" customHeight="1">
-      <c r="A83" s="36" t="s">
-        <v>358</v>
-      </c>
-      <c r="B83" s="37" t="s">
-        <v>359</v>
+      <c r="A83" s="35" t="s">
+        <v>350</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>351</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="E83" s="11"/>
-      <c r="F83" s="37"/>
+        <v>352</v>
+      </c>
+      <c r="E83" s="26" t="s">
+        <v>485</v>
+      </c>
+      <c r="F83" s="36"/>
       <c r="G83" s="11"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
+      <c r="H83" s="36"/>
+      <c r="I83" s="36"/>
     </row>
     <row r="84" spans="1:9" ht="36" customHeight="1">
-      <c r="A84" s="36" t="s">
-        <v>361</v>
-      </c>
-      <c r="B84" s="37" t="s">
-        <v>362</v>
+      <c r="A84" s="35" t="s">
+        <v>353</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>354</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="E84" s="11"/>
-      <c r="F84" s="37"/>
+        <v>355</v>
+      </c>
+      <c r="E84" s="26" t="s">
+        <v>486</v>
+      </c>
+      <c r="F84" s="36"/>
       <c r="G84" s="11"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="36"/>
     </row>
     <row r="85" spans="1:9" ht="36" customHeight="1">
-      <c r="A85" s="52"/>
-      <c r="B85" s="53"/>
-      <c r="C85" s="54"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="53"/>
+      <c r="A85" s="51"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="52"/>
+      <c r="E85" s="52"/>
+      <c r="F85" s="52"/>
+      <c r="G85" s="52"/>
+      <c r="H85" s="52"/>
       <c r="I85" s="7" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="36" customHeight="1">
-      <c r="A86" s="38" t="s">
-        <v>365</v>
-      </c>
-      <c r="B86" s="39" t="s">
-        <v>366</v>
+      <c r="A86" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="B86" s="38" t="s">
+        <v>358</v>
       </c>
       <c r="C86" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="E86" s="39" t="s">
-        <v>368</v>
-      </c>
-      <c r="F86" s="39"/>
+        <v>359</v>
+      </c>
+      <c r="E86" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="F86" s="38"/>
       <c r="G86" s="11"/>
-      <c r="H86" s="39"/>
-      <c r="I86" s="39" t="s">
-        <v>124</v>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="36" customHeight="1">
-      <c r="A87" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="B87" s="39" t="s">
-        <v>370</v>
+      <c r="A87" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="B87" s="38" t="s">
+        <v>362</v>
       </c>
       <c r="C87" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="E87" s="11"/>
-      <c r="F87" s="39"/>
-      <c r="G87" s="11"/>
-      <c r="H87" s="39"/>
-      <c r="I87" s="39"/>
+        <v>246</v>
+      </c>
+      <c r="E87" s="26" t="s">
+        <v>487</v>
+      </c>
+      <c r="F87" s="57" t="s">
+        <v>490</v>
+      </c>
+      <c r="G87" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="H87" s="38"/>
+      <c r="I87" s="38"/>
     </row>
     <row r="88" spans="1:9" ht="36" customHeight="1">
-      <c r="A88" s="38" t="s">
-        <v>371</v>
-      </c>
-      <c r="B88" s="39" t="s">
-        <v>372</v>
+      <c r="A88" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="B88" s="38" t="s">
+        <v>364</v>
       </c>
       <c r="C88" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="E88" s="11"/>
-      <c r="F88" s="39"/>
+        <v>365</v>
+      </c>
+      <c r="E88" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="F88" s="38"/>
       <c r="G88" s="11"/>
-      <c r="H88" s="39"/>
-      <c r="I88" s="39"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="38"/>
     </row>
     <row r="89" spans="1:9" ht="36" customHeight="1">
-      <c r="A89" s="38" t="s">
-        <v>374</v>
-      </c>
-      <c r="B89" s="39" t="s">
-        <v>375</v>
+      <c r="A89" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="B89" s="38" t="s">
+        <v>367</v>
       </c>
       <c r="C89" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="E89" s="11"/>
-      <c r="F89" s="39"/>
+        <v>368</v>
+      </c>
+      <c r="E89" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="F89" s="38"/>
       <c r="G89" s="11"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="38"/>
     </row>
     <row r="90" spans="1:9" ht="36" customHeight="1">
-      <c r="A90" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="B90" s="39" t="s">
-        <v>378</v>
+      <c r="A90" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="B90" s="38" t="s">
+        <v>370</v>
       </c>
       <c r="C90" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="E90" s="11"/>
-      <c r="F90" s="39"/>
+        <v>371</v>
+      </c>
+      <c r="E90" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="F90" s="38"/>
       <c r="G90" s="11"/>
-      <c r="H90" s="39"/>
-      <c r="I90" s="39"/>
+      <c r="H90" s="38"/>
+      <c r="I90" s="38"/>
     </row>
     <row r="91" spans="1:9" ht="36" customHeight="1">
-      <c r="A91" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="B91" s="39" t="s">
-        <v>381</v>
+      <c r="A91" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="B91" s="38" t="s">
+        <v>373</v>
       </c>
       <c r="C91" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="E91" s="11"/>
-      <c r="F91" s="39"/>
+        <v>374</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>494</v>
+      </c>
+      <c r="F91" s="38"/>
       <c r="G91" s="11"/>
-      <c r="H91" s="39"/>
-      <c r="I91" s="39"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="38"/>
     </row>
     <row r="92" spans="1:9" ht="36" customHeight="1">
-      <c r="A92" s="38" t="s">
-        <v>383</v>
-      </c>
-      <c r="B92" s="39" t="s">
-        <v>384</v>
+      <c r="A92" s="37" t="s">
+        <v>375</v>
+      </c>
+      <c r="B92" s="38" t="s">
+        <v>376</v>
       </c>
       <c r="C92" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="39"/>
+        <v>377</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="F92" s="38"/>
       <c r="G92" s="11"/>
-      <c r="H92" s="39"/>
-      <c r="I92" s="39"/>
+      <c r="H92" s="38"/>
+      <c r="I92" s="38"/>
     </row>
     <row r="93" spans="1:9" ht="36" customHeight="1">
-      <c r="A93" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="B93" s="39" t="s">
-        <v>387</v>
+      <c r="A93" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="B93" s="38" t="s">
+        <v>379</v>
       </c>
       <c r="C93" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="E93" s="39" t="s">
-        <v>389</v>
-      </c>
-      <c r="F93" s="39"/>
+        <v>380</v>
+      </c>
+      <c r="E93" s="58" t="s">
+        <v>496</v>
+      </c>
+      <c r="F93" s="38"/>
       <c r="G93" s="11"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="39" t="s">
-        <v>390</v>
+      <c r="H93" s="38"/>
+      <c r="I93" s="38" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1">
-      <c r="A94" s="52"/>
-      <c r="B94" s="53"/>
-      <c r="C94" s="54"/>
-      <c r="D94" s="53"/>
-      <c r="E94" s="53"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="53"/>
-      <c r="H94" s="53"/>
+      <c r="A94" s="51"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="53"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="52"/>
       <c r="I94" s="7" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="36" customHeight="1">
-      <c r="A95" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="B95" s="39" t="s">
-        <v>393</v>
+      <c r="A95" s="37" t="s">
+        <v>383</v>
+      </c>
+      <c r="B95" s="38" t="s">
+        <v>384</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="E95" s="11"/>
-      <c r="F95" s="39"/>
+        <v>385</v>
+      </c>
+      <c r="E95" s="26" t="s">
+        <v>497</v>
+      </c>
+      <c r="F95" s="38"/>
       <c r="G95" s="11"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="39"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="38"/>
     </row>
     <row r="96" spans="1:9" ht="36" customHeight="1">
-      <c r="A96" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="B96" s="39" t="s">
-        <v>396</v>
+      <c r="A96" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="B96" s="38" t="s">
+        <v>387</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="E96" s="11"/>
-      <c r="F96" s="39"/>
+        <v>388</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="F96" s="38"/>
       <c r="G96" s="11"/>
-      <c r="H96" s="39"/>
-      <c r="I96" s="39"/>
+      <c r="H96" s="38"/>
+      <c r="I96" s="38"/>
     </row>
     <row r="97" spans="1:9" ht="36" customHeight="1">
-      <c r="A97" s="38" t="s">
-        <v>398</v>
-      </c>
-      <c r="B97" s="39" t="s">
-        <v>252</v>
+      <c r="A97" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="B97" s="38" t="s">
+        <v>246</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="E97" s="11"/>
-      <c r="F97" s="39"/>
-      <c r="G97" s="11"/>
-      <c r="H97" s="39"/>
-      <c r="I97" s="39"/>
+        <v>390</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>487</v>
+      </c>
+      <c r="F97" s="57" t="s">
+        <v>490</v>
+      </c>
+      <c r="G97" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="H97" s="38"/>
+      <c r="I97" s="38"/>
     </row>
     <row r="98" spans="1:9" ht="36" customHeight="1">
-      <c r="A98" s="38" t="s">
-        <v>400</v>
-      </c>
-      <c r="B98" s="39" t="s">
-        <v>401</v>
+      <c r="A98" s="37" t="s">
+        <v>391</v>
+      </c>
+      <c r="B98" s="38" t="s">
+        <v>392</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="E98" s="11"/>
-      <c r="F98" s="39"/>
+        <v>393</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="F98" s="38"/>
       <c r="G98" s="11"/>
-      <c r="H98" s="39"/>
-      <c r="I98" s="39"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="38"/>
     </row>
     <row r="99" spans="1:9" ht="36" customHeight="1">
-      <c r="A99" s="38" t="s">
-        <v>403</v>
-      </c>
-      <c r="B99" s="39" t="s">
-        <v>404</v>
+      <c r="A99" s="37" t="s">
+        <v>394</v>
+      </c>
+      <c r="B99" s="38" t="s">
+        <v>395</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="39"/>
+        <v>396</v>
+      </c>
+      <c r="E99" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="F99" s="38"/>
       <c r="G99" s="11"/>
-      <c r="H99" s="39"/>
-      <c r="I99" s="39"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="38"/>
     </row>
     <row r="100" spans="1:9" ht="36" customHeight="1">
-      <c r="A100" s="38" t="s">
-        <v>406</v>
-      </c>
-      <c r="B100" s="39" t="s">
-        <v>373</v>
+      <c r="A100" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="B100" s="38" t="s">
+        <v>365</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="E100" s="11"/>
-      <c r="F100" s="39"/>
+        <v>398</v>
+      </c>
+      <c r="E100" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="F100" s="38"/>
       <c r="G100" s="11"/>
-      <c r="H100" s="39"/>
-      <c r="I100" s="39"/>
+      <c r="H100" s="38"/>
+      <c r="I100" s="38"/>
     </row>
     <row r="101" spans="1:9" ht="36" customHeight="1">
-      <c r="A101" s="38" t="s">
-        <v>408</v>
-      </c>
-      <c r="B101" s="39" t="s">
-        <v>409</v>
+      <c r="A101" s="37" t="s">
+        <v>399</v>
+      </c>
+      <c r="B101" s="38" t="s">
+        <v>400</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="39"/>
+        <v>401</v>
+      </c>
+      <c r="E101" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="F101" s="38"/>
       <c r="G101" s="11"/>
-      <c r="H101" s="39"/>
-      <c r="I101" s="39"/>
+      <c r="H101" s="38"/>
+      <c r="I101" s="38"/>
     </row>
     <row r="102" spans="1:9" ht="36" customHeight="1">
-      <c r="A102" s="38" t="s">
-        <v>411</v>
-      </c>
-      <c r="B102" s="39" t="s">
-        <v>385</v>
+      <c r="A102" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="B102" s="38" t="s">
+        <v>377</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="E102" s="11"/>
-      <c r="F102" s="39"/>
+        <v>403</v>
+      </c>
+      <c r="E102" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="F102" s="38"/>
       <c r="G102" s="11"/>
-      <c r="H102" s="39"/>
-      <c r="I102" s="39"/>
+      <c r="H102" s="38"/>
+      <c r="I102" s="38"/>
     </row>
     <row r="103" spans="1:9" ht="36" customHeight="1">
-      <c r="A103" s="38" t="s">
-        <v>413</v>
-      </c>
-      <c r="B103" s="39" t="s">
-        <v>414</v>
+      <c r="A103" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="B103" s="38" t="s">
+        <v>405</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="E103" s="11"/>
-      <c r="F103" s="39"/>
+        <v>406</v>
+      </c>
+      <c r="E103" s="26" t="s">
+        <v>494</v>
+      </c>
+      <c r="F103" s="38"/>
       <c r="G103" s="11"/>
-      <c r="H103" s="39"/>
-      <c r="I103" s="39"/>
+      <c r="H103" s="38"/>
+      <c r="I103" s="38"/>
     </row>
     <row r="104" spans="1:9" ht="36" customHeight="1">
-      <c r="A104" s="38" t="s">
-        <v>416</v>
-      </c>
-      <c r="B104" s="39" t="s">
-        <v>417</v>
+      <c r="A104" s="37" t="s">
+        <v>407</v>
+      </c>
+      <c r="B104" s="38" t="s">
+        <v>408</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="E104" s="11"/>
-      <c r="F104" s="39"/>
+        <v>409</v>
+      </c>
+      <c r="E104" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="F104" s="38"/>
       <c r="G104" s="11"/>
-      <c r="H104" s="39"/>
-      <c r="I104" s="39"/>
+      <c r="H104" s="38"/>
+      <c r="I104" s="38"/>
     </row>
     <row r="105" spans="1:9" ht="36" customHeight="1">
-      <c r="A105" s="38" t="s">
-        <v>419</v>
-      </c>
-      <c r="B105" s="39" t="s">
-        <v>420</v>
+      <c r="A105" s="37" t="s">
+        <v>410</v>
+      </c>
+      <c r="B105" s="38" t="s">
+        <v>411</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="E105" s="11"/>
-      <c r="F105" s="39"/>
+        <v>412</v>
+      </c>
+      <c r="E105" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="F105" s="38"/>
       <c r="G105" s="11"/>
-      <c r="H105" s="39"/>
-      <c r="I105" s="39"/>
+      <c r="H105" s="38"/>
+      <c r="I105" s="38"/>
     </row>
     <row r="106" spans="1:9" ht="36" customHeight="1">
-      <c r="A106" s="52"/>
-      <c r="B106" s="53"/>
-      <c r="C106" s="54"/>
-      <c r="D106" s="53"/>
-      <c r="E106" s="53"/>
-      <c r="F106" s="53"/>
-      <c r="G106" s="53"/>
-      <c r="H106" s="53"/>
+      <c r="A106" s="51"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="52"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
+      <c r="H106" s="52"/>
       <c r="I106" s="7" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="36" customHeight="1">
-      <c r="A107" s="40" t="s">
-        <v>423</v>
-      </c>
-      <c r="B107" s="41" t="s">
-        <v>424</v>
+      <c r="A107" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="B107" s="40" t="s">
+        <v>415</v>
       </c>
       <c r="C107" t="s">
-        <v>467</v>
-      </c>
-      <c r="D107" s="26" t="s">
-        <v>466</v>
-      </c>
-      <c r="E107" s="41" t="s">
-        <v>425</v>
-      </c>
-      <c r="F107" s="41"/>
+        <v>458</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="E107" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="F107" s="40"/>
       <c r="G107" s="11"/>
-      <c r="H107" s="41"/>
-      <c r="I107" s="41" t="s">
-        <v>124</v>
+      <c r="H107" s="40"/>
+      <c r="I107" s="40" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="36" customHeight="1">
-      <c r="A108" s="40" t="s">
-        <v>426</v>
-      </c>
-      <c r="B108" s="41" t="s">
-        <v>427</v>
+      <c r="A108" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="B108" s="40" t="s">
+        <v>418</v>
       </c>
       <c r="C108" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="E108" s="11"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="11"/>
-      <c r="H108" s="41"/>
-      <c r="I108" s="41"/>
+        <v>239</v>
+      </c>
+      <c r="E108" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="F108" s="59" t="s">
+        <v>505</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="H108" s="59" t="s">
+        <v>506</v>
+      </c>
+      <c r="I108" s="40"/>
     </row>
     <row r="109" spans="1:9" ht="36" customHeight="1">
-      <c r="A109" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="B109" s="41" t="s">
-        <v>429</v>
+      <c r="A109" s="39" t="s">
+        <v>419</v>
+      </c>
+      <c r="B109" s="40" t="s">
+        <v>420</v>
       </c>
       <c r="C109" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="E109" s="11"/>
-      <c r="F109" s="41"/>
+        <v>421</v>
+      </c>
+      <c r="E109" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="F109" s="40"/>
       <c r="G109" s="11"/>
-      <c r="H109" s="41"/>
-      <c r="I109" s="41"/>
+      <c r="H109" s="40"/>
+      <c r="I109" s="40"/>
     </row>
     <row r="110" spans="1:9" ht="36" customHeight="1">
-      <c r="A110" s="40" t="s">
-        <v>431</v>
-      </c>
-      <c r="B110" s="41" t="s">
-        <v>432</v>
+      <c r="A110" s="39" t="s">
+        <v>422</v>
+      </c>
+      <c r="B110" s="40" t="s">
+        <v>423</v>
       </c>
       <c r="C110" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="E110" s="11"/>
-      <c r="F110" s="41"/>
+        <v>424</v>
+      </c>
+      <c r="E110" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="F110" s="40"/>
       <c r="G110" s="11"/>
-      <c r="H110" s="41"/>
-      <c r="I110" s="41"/>
+      <c r="H110" s="40"/>
+      <c r="I110" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A94:H94"/>
     <mergeCell ref="A106:H106"/>
     <mergeCell ref="A53:H53"/>
@@ -14759,8 +19727,19 @@
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{3E973F3D-7F90-47C5-BA46-CD1485089CF1}"/>
+    <hyperlink ref="I4" r:id="rId2" xr:uid="{A5A5C564-C1F4-433B-911C-EAC646805F5F}"/>
+    <hyperlink ref="I5" r:id="rId3" xr:uid="{B6064F80-99B0-4BA2-9B35-4B63C685BCDE}"/>
+    <hyperlink ref="I7" r:id="rId4" xr:uid="{A360ECF7-B7BA-4222-BCFD-FF479230197A}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14776,13 +19755,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>434</v>
+      <c r="A1" s="41" t="s">
+        <v>425</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C1" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
     </row>
@@ -14790,139 +19769,139 @@
       <c r="A2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="43">
+      <c r="B2" s="42">
         <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.95" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="B3" s="44">
+        <v>428</v>
+      </c>
+      <c r="B3" s="43">
         <v>3</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.95" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="B4" s="44">
+        <v>430</v>
+      </c>
+      <c r="B4" s="43">
         <v>6</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="B5" s="45">
+      <c r="A5" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="B5" s="44">
         <v>17</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>442</v>
+      <c r="C5" s="22" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A6" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="B6" s="45">
+      <c r="A6" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="B6" s="44">
         <v>14</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>444</v>
+      <c r="C6" s="22" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A7" s="32" t="s">
-        <v>445</v>
-      </c>
-      <c r="B7" s="46">
+      <c r="A7" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="B7" s="45">
         <v>9</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>446</v>
+      <c r="C7" s="31" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A8" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="B8" s="47">
+      <c r="A8" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="46">
         <v>9</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>448</v>
+      <c r="C8" s="34" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A9" s="35" t="s">
-        <v>449</v>
-      </c>
-      <c r="B9" s="47">
+      <c r="A9" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="B9" s="46">
         <v>6</v>
       </c>
-      <c r="C9" s="35" t="s">
-        <v>450</v>
+      <c r="C9" s="34" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A10" s="37" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="48">
+      <c r="A10" s="36" t="s">
+        <v>442</v>
+      </c>
+      <c r="B10" s="47">
         <v>4</v>
       </c>
-      <c r="C10" s="37" t="s">
-        <v>452</v>
+      <c r="C10" s="36" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A11" s="39" t="s">
-        <v>453</v>
-      </c>
-      <c r="B11" s="49">
+      <c r="A11" s="38" t="s">
+        <v>444</v>
+      </c>
+      <c r="B11" s="48">
         <v>8</v>
       </c>
-      <c r="C11" s="39" t="s">
-        <v>454</v>
+      <c r="C11" s="38" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A12" s="39" t="s">
-        <v>455</v>
-      </c>
-      <c r="B12" s="49">
+      <c r="A12" s="38" t="s">
+        <v>446</v>
+      </c>
+      <c r="B12" s="48">
         <v>11</v>
       </c>
-      <c r="C12" s="39" t="s">
-        <v>456</v>
+      <c r="C12" s="38" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="21.95" customHeight="1">
-      <c r="A13" s="41" t="s">
-        <v>457</v>
-      </c>
-      <c r="B13" s="50">
+      <c r="A13" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="B13" s="49">
         <v>4</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>458</v>
+      <c r="C13" s="40" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21.95" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B14" s="51">
+        <v>450</v>
+      </c>
+      <c r="B14" s="50">
         <f>SUM(B2:B13)</f>
         <v>97</v>
       </c>

--- a/LINE_Bot_內容對照表.xlsx
+++ b/LINE_Bot_內容對照表.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93295951-C1A6-48FF-883F-ADB4EC8547D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EBAB5B-6DEF-483E-9A85-65744D4A0090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="說明" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="511">
   <si>
     <t>欄位說明</t>
   </si>
@@ -16502,12 +16502,39 @@
     </r>
     <phoneticPr fontId="24" type="noConversion"/>
   </si>
+  <si>
+    <t>地價底圖.png</t>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>資訊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>底圖.png</t>
+    </r>
+    <phoneticPr fontId="24" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16690,6 +16717,21 @@
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -16792,7 +16834,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -16940,11 +16982,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -16963,6 +17000,12 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -17516,7 +17559,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
@@ -17525,7 +17568,7 @@
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.95" customHeight="1">
+    <row r="1" spans="1:9" ht="27.9" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -17555,14 +17598,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="36" customHeight="1">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
       <c r="I2" s="7" t="s">
         <v>53</v>
       </c>
@@ -17571,7 +17614,7 @@
       <c r="A3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="52" t="s">
         <v>472</v>
       </c>
       <c r="D3" s="10" t="s">
@@ -17583,7 +17626,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="11"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="51" t="s">
         <v>464</v>
       </c>
     </row>
@@ -17591,7 +17634,7 @@
       <c r="A4" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="52" t="s">
         <v>466</v>
       </c>
       <c r="D4" s="10" t="s">
@@ -17603,7 +17646,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="11"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="54" t="s">
+      <c r="I4" s="51" t="s">
         <v>465</v>
       </c>
     </row>
@@ -17611,7 +17654,7 @@
       <c r="A5" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="52" t="s">
         <v>467</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -17623,7 +17666,7 @@
       <c r="F5" s="9"/>
       <c r="G5" s="11"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="54" t="s">
+      <c r="I5" s="51" t="s">
         <v>468</v>
       </c>
     </row>
@@ -17631,7 +17674,7 @@
       <c r="A6" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="55" t="s">
+      <c r="B6" s="52" t="s">
         <v>469</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -17651,7 +17694,7 @@
       <c r="A7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="52" t="s">
         <v>473</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -17663,7 +17706,7 @@
       <c r="F7" s="9"/>
       <c r="G7" s="11"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="54" t="s">
+      <c r="I7" s="51" t="s">
         <v>470</v>
       </c>
     </row>
@@ -17671,7 +17714,7 @@
       <c r="A8" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="55" t="s">
+      <c r="B8" s="52" t="s">
         <v>471</v>
       </c>
       <c r="D8" s="10" t="s">
@@ -17688,14 +17731,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1">
-      <c r="A9" s="51"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="52"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
       <c r="I9" s="7" t="s">
         <v>74</v>
       </c>
@@ -17759,14 +17802,14 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
       <c r="I13" s="7" t="s">
         <v>87</v>
       </c>
@@ -17892,14 +17935,14 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="36" customHeight="1">
-      <c r="A20" s="51"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="52"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
       <c r="I20" s="7" t="s">
         <v>112</v>
       </c>
@@ -18288,14 +18331,14 @@
       <c r="I37" s="22"/>
     </row>
     <row r="38" spans="1:9" ht="36" customHeight="1">
-      <c r="A38" s="51"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
       <c r="I38" s="7" t="s">
         <v>194</v>
       </c>
@@ -18575,14 +18618,14 @@
       <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:9" ht="36" customHeight="1">
-      <c r="A53" s="51"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="52"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
       <c r="I53" s="7" t="s">
         <v>255</v>
       </c>
@@ -18791,14 +18834,14 @@
       <c r="I62" s="31"/>
     </row>
     <row r="63" spans="1:9" ht="36" customHeight="1">
-      <c r="A63" s="51"/>
-      <c r="B63" s="52"/>
-      <c r="C63" s="53"/>
-      <c r="D63" s="52"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="52"/>
-      <c r="H63" s="52"/>
+      <c r="A63" s="57"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
       <c r="I63" s="7" t="s">
         <v>295</v>
       </c>
@@ -18881,7 +18924,7 @@
       <c r="D67" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="E67" s="56" t="s">
+      <c r="E67" s="53" t="s">
         <v>477</v>
       </c>
       <c r="F67" s="34"/>
@@ -18985,7 +19028,7 @@
         <v>323</v>
       </c>
       <c r="C72" t="s">
-        <v>461</v>
+        <v>509</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>324</v>
@@ -18999,14 +19042,14 @@
       <c r="I72" s="34"/>
     </row>
     <row r="73" spans="1:9" ht="36" customHeight="1">
-      <c r="A73" s="51"/>
-      <c r="B73" s="52"/>
-      <c r="C73" s="53"/>
-      <c r="D73" s="52"/>
-      <c r="E73" s="52"/>
-      <c r="F73" s="52"/>
-      <c r="G73" s="52"/>
-      <c r="H73" s="52"/>
+      <c r="A73" s="57"/>
+      <c r="B73" s="58"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="58"/>
+      <c r="H73" s="58"/>
       <c r="I73" s="7" t="s">
         <v>325</v>
       </c>
@@ -19120,14 +19163,14 @@
       <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:9" ht="36" customHeight="1">
-      <c r="A80" s="51"/>
-      <c r="B80" s="52"/>
-      <c r="C80" s="53"/>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="52"/>
-      <c r="H80" s="52"/>
+      <c r="A80" s="57"/>
+      <c r="B80" s="58"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="58"/>
+      <c r="E80" s="58"/>
+      <c r="F80" s="58"/>
+      <c r="G80" s="58"/>
+      <c r="H80" s="58"/>
       <c r="I80" s="7" t="s">
         <v>342</v>
       </c>
@@ -19161,6 +19204,9 @@
       </c>
       <c r="B82" s="36" t="s">
         <v>348</v>
+      </c>
+      <c r="C82" s="60" t="s">
+        <v>510</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>349</v>
@@ -19180,6 +19226,9 @@
       <c r="B83" s="36" t="s">
         <v>351</v>
       </c>
+      <c r="C83" s="60" t="s">
+        <v>510</v>
+      </c>
       <c r="D83" s="10" t="s">
         <v>352</v>
       </c>
@@ -19198,6 +19247,9 @@
       <c r="B84" s="36" t="s">
         <v>354</v>
       </c>
+      <c r="C84" s="60" t="s">
+        <v>510</v>
+      </c>
       <c r="D84" s="10" t="s">
         <v>355</v>
       </c>
@@ -19210,14 +19262,14 @@
       <c r="I84" s="36"/>
     </row>
     <row r="85" spans="1:9" ht="36" customHeight="1">
-      <c r="A85" s="51"/>
-      <c r="B85" s="52"/>
-      <c r="C85" s="53"/>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="52"/>
-      <c r="H85" s="52"/>
+      <c r="A85" s="57"/>
+      <c r="B85" s="58"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="58"/>
+      <c r="G85" s="58"/>
+      <c r="H85" s="58"/>
       <c r="I85" s="7" t="s">
         <v>356</v>
       </c>
@@ -19261,7 +19313,7 @@
       <c r="E87" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="F87" s="57" t="s">
+      <c r="F87" s="54" t="s">
         <v>490</v>
       </c>
       <c r="G87" s="26" t="s">
@@ -19388,7 +19440,7 @@
       <c r="D93" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="E93" s="58" t="s">
+      <c r="E93" s="55" t="s">
         <v>496</v>
       </c>
       <c r="F93" s="38"/>
@@ -19399,14 +19451,14 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1">
-      <c r="A94" s="51"/>
-      <c r="B94" s="52"/>
-      <c r="C94" s="53"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="52"/>
+      <c r="A94" s="57"/>
+      <c r="B94" s="58"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="58"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="58"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="58"/>
       <c r="I94" s="7" t="s">
         <v>382</v>
       </c>
@@ -19460,7 +19512,7 @@
       <c r="E97" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="F97" s="57" t="s">
+      <c r="F97" s="54" t="s">
         <v>490</v>
       </c>
       <c r="G97" s="26" t="s">
@@ -19614,14 +19666,14 @@
       <c r="I105" s="38"/>
     </row>
     <row r="106" spans="1:9" ht="36" customHeight="1">
-      <c r="A106" s="51"/>
-      <c r="B106" s="52"/>
-      <c r="C106" s="53"/>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
-      <c r="H106" s="52"/>
+      <c r="A106" s="57"/>
+      <c r="B106" s="58"/>
+      <c r="C106" s="59"/>
+      <c r="D106" s="58"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="58"/>
+      <c r="G106" s="58"/>
+      <c r="H106" s="58"/>
       <c r="I106" s="7" t="s">
         <v>413</v>
       </c>
@@ -19665,13 +19717,13 @@
       <c r="E108" s="26" t="s">
         <v>503</v>
       </c>
-      <c r="F108" s="59" t="s">
+      <c r="F108" s="56" t="s">
         <v>505</v>
       </c>
       <c r="G108" s="26" t="s">
         <v>504</v>
       </c>
-      <c r="H108" s="59" t="s">
+      <c r="H108" s="56" t="s">
         <v>506</v>
       </c>
       <c r="I108" s="40"/>
@@ -19720,6 +19772,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A94:H94"/>
     <mergeCell ref="A106:H106"/>
     <mergeCell ref="A53:H53"/>
@@ -19727,11 +19784,6 @@
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
   </mergeCells>
   <phoneticPr fontId="24" type="noConversion"/>
   <hyperlinks>
@@ -19754,7 +19806,7 @@
     <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.95" customHeight="1">
+    <row r="1" spans="1:3" ht="21.9" customHeight="1">
       <c r="A1" s="41" t="s">
         <v>425</v>
       </c>
@@ -19765,7 +19817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="21.95" customHeight="1">
+    <row r="2" spans="1:3" ht="21.9" customHeight="1">
       <c r="A2" s="9" t="s">
         <v>51</v>
       </c>
@@ -19776,7 +19828,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="21.95" customHeight="1">
+    <row r="3" spans="1:3" ht="21.9" customHeight="1">
       <c r="A3" s="13" t="s">
         <v>428</v>
       </c>
@@ -19787,7 +19839,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21.95" customHeight="1">
+    <row r="4" spans="1:3" ht="21.9" customHeight="1">
       <c r="A4" s="13" t="s">
         <v>430</v>
       </c>
@@ -19798,7 +19850,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.95" customHeight="1">
+    <row r="5" spans="1:3" ht="21.9" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>432</v>
       </c>
@@ -19809,7 +19861,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.95" customHeight="1">
+    <row r="6" spans="1:3" ht="21.9" customHeight="1">
       <c r="A6" s="22" t="s">
         <v>434</v>
       </c>
@@ -19820,7 +19872,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="21.95" customHeight="1">
+    <row r="7" spans="1:3" ht="21.9" customHeight="1">
       <c r="A7" s="31" t="s">
         <v>436</v>
       </c>
@@ -19831,7 +19883,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="21.95" customHeight="1">
+    <row r="8" spans="1:3" ht="21.9" customHeight="1">
       <c r="A8" s="34" t="s">
         <v>438</v>
       </c>
@@ -19842,7 +19894,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="21.95" customHeight="1">
+    <row r="9" spans="1:3" ht="21.9" customHeight="1">
       <c r="A9" s="34" t="s">
         <v>440</v>
       </c>
@@ -19853,7 +19905,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="21.95" customHeight="1">
+    <row r="10" spans="1:3" ht="21.9" customHeight="1">
       <c r="A10" s="36" t="s">
         <v>442</v>
       </c>
@@ -19864,7 +19916,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="21.95" customHeight="1">
+    <row r="11" spans="1:3" ht="21.9" customHeight="1">
       <c r="A11" s="38" t="s">
         <v>444</v>
       </c>
@@ -19875,7 +19927,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21.95" customHeight="1">
+    <row r="12" spans="1:3" ht="21.9" customHeight="1">
       <c r="A12" s="38" t="s">
         <v>446</v>
       </c>
@@ -19886,7 +19938,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="21.95" customHeight="1">
+    <row r="13" spans="1:3" ht="21.9" customHeight="1">
       <c r="A13" s="40" t="s">
         <v>448</v>
       </c>
@@ -19897,7 +19949,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="21.95" customHeight="1">
+    <row r="14" spans="1:3" ht="21.9" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>450</v>
       </c>

--- a/LINE_Bot_內容對照表.xlsx
+++ b/LINE_Bot_內容對照表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30EBAB5B-6DEF-483E-9A85-65744D4A0090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188F4A14-A296-4061-AC52-35AB68F19DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="510">
   <si>
     <t>欄位說明</t>
   </si>
@@ -11372,254 +11372,48 @@
     <t>合計</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>登記業務諮詢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">.png
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-      </rPr>
-      <t>測量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>業務諮詢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">.png
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-      </rPr>
-      <t>地價</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>業務諮詢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">.png
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>資訊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>業務諮詢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">.png
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-      </rPr>
-      <t>地用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>業務諮詢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">.png
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="3"/>
-      </rPr>
-      <t>檔案應用其他綜合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>業務諮詢</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>.png</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>登記業務諮詢.png</t>
-  </si>
-  <si>
-    <t>測量業務諮詢.png</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>地價業務諮詢.png</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>資訊業務諮詢.png</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>地用業務諮詢.png</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
     <t>檔案應用其他綜合業務諮詢</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>檔案應用其他綜合業務諮詢.png</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>登記底圖.png</t>
-  </si>
-  <si>
-    <t>測量底圖.png</t>
-  </si>
-  <si>
-    <t>地價底圖.png</t>
-  </si>
-  <si>
-    <t>地用底圖.png</t>
-  </si>
-  <si>
-    <t>檔案應用底圖.png</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>https://sinhu.land.hsinchu.gov.tw/</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>https://land.hsinchu.gov.tw/valueprice/?mode=queryCasedo_show&amp;parent_id=10309&amp;type_id=10309</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>查詢案件辦理情形</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>線上取號</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>https://sinhu.land.hsinchu.gov.tw/jhubei_waitNum/?mode=add&amp;parent_id=10475&amp;type_id=10475</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>臉書粉專</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>https://sinhu.land.hsinchu.gov.tw/content/?parent_id=10338&amp;type_id=10338</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>邀請好友</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>官方網站</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>預約服務</t>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -11943,7 +11737,7 @@
       </rPr>
       <t>(two hearts)</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12067,7 +11861,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12137,7 +11931,7 @@
       </rPr>
       <t>。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12404,7 +12198,7 @@
       </rPr>
       <t>】實價登錄查詢網站</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12528,7 +12322,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12636,7 +12430,7 @@
       </rPr>
       <t>預售屋解約。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12722,7 +12516,7 @@
       </rPr>
       <t>內完成申報。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12837,7 +12631,7 @@
       </rPr>
       <t xml:space="preserve"> https://e91plus.tycg.gov.tw/Index</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -12869,7 +12663,7 @@
       </rPr>
       <t>租賃及預售屋實價登錄案件可分為「憑證登錄，線上申報」、「線上登錄，紙本送件」及「紙本申報」三種方式，提醒您若採「線上登錄，紙本送件」及「紙本申報」兩種方式申報，需於申報期限內將紙本資料送至地政事務所收件，才能完成申報手續。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -13039,7 +12833,7 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -13369,7 +13163,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -13661,7 +13455,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -13749,7 +13543,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -13872,7 +13666,7 @@
       </rPr>
       <t>曾於該建物設籍之戶籍謄本、繳納房屋稅籍證明、用電證明或繳納自來水費用證明、建物完工證明書或其他證明文件。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14198,7 +13992,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14230,7 +14024,7 @@
       </rPr>
       <t>.jpg</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14254,7 +14048,7 @@
       </rPr>
       <t>.jpg</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14286,7 +14080,7 @@
       </rPr>
       <t>辦理變更編定，請檢具下列資料向土地所在地縣市政府地政局申請：變更編定申請書、興辦事業計畫核准文件、變更編定同意書、土地登記簿謄本及地籍圖謄本、土地使用計畫配置圖及位置圖。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14327,7 +14121,7 @@
       <t xml:space="preserve">
 https://moiref.moi.gov.tw/pubref/</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14395,7 +14189,7 @@
       </rPr>
       <t>https://up.tcd.gov.tw/Ex3S/ExWeb.aspx</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14463,7 +14257,7 @@
       </rPr>
       <t>萬罰鍰。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -14521,7 +14315,7 @@
       </rPr>
       <t>https://law.moj.gov.tw/LawClass/LawSingle.aspx?pcode=D0060013&amp;flno=6</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15002,7 +14796,7 @@
       </rPr>
       <t>】建管時間</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15034,7 +14828,7 @@
       </rPr>
       <t>土地謄本載有使用分區及使用地類別之土地即為非都市土地，反之即為都市土地。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15066,7 +14860,7 @@
       </rPr>
       <t>非都市土地依其使用分區之性質，編定為甲種建築、乙種建築、丙種建築、丁種建築、農牧、林業、養殖、鹽業、礦業、窯業、交通、水利、遊憩、古蹟保存、生態保護、國土保安、殯葬、海域、特定目的事業等使用地。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15392,7 +15186,7 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15424,7 +15218,7 @@
       </rPr>
       <t>年起地目等則制度已廢除，無法辦理地目變更相關業務。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15456,7 +15250,7 @@
       </rPr>
       <t>地目等則已經廢除，土地謄本上不再顯示土地使用分區及使用地類別相關資料，如需查詢地目等則資料可向地政事務所申請人工登記簿謄本或地籍整理清冊。</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15815,7 +15609,7 @@
       </rPr>
       <t>日</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -15874,7 +15668,7 @@
       <t xml:space="preserve">
 https://www.zhongli-land.tycg.gov.tw/archive_QA.htm</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -16063,7 +15857,7 @@
       <t xml:space="preserve">
 https://www.asuswebstorage.com/navigate/a/#/s/9578C16467DC4329B9BF12B95B74768F6</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -16087,7 +15881,7 @@
       </rPr>
       <t>.jpg</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -16111,7 +15905,7 @@
       </rPr>
       <t>.jpg</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -16269,7 +16063,7 @@
       </rPr>
       <t>https://www.zhongli-land.tycg.gov.tw/cl.aspx?n=5563</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -16500,41 +16294,58 @@
       </rPr>
       <t>，將有專人進一步協助您，謝謝您！</t>
     </r>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <t>地價底圖.png</t>
-    <phoneticPr fontId="24" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>資訊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="新細明體"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>底圖.png</t>
-    </r>
-    <phoneticPr fontId="24" type="noConversion"/>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>登記業務諮詢.jpg
+測量業務諮詢.jpg
+地價業務諮詢.jpg
+資訊業務諮詢.jpg
+地用業務諮詢.jpg
+檔案應用其他綜合業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>登記業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>登記底圖.jpg</t>
+  </si>
+  <si>
+    <t>測量業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>測量底圖.jpg</t>
+  </si>
+  <si>
+    <t>地價業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>地價底圖.jpg</t>
+  </si>
+  <si>
+    <t>資訊業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>資訊底圖.jpg</t>
+  </si>
+  <si>
+    <t>地用業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>地用底圖.jpg</t>
+  </si>
+  <si>
+    <t>檔案應用其他綜合業務諮詢.jpg</t>
+  </si>
+  <si>
+    <t>檔案應用底圖.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16672,19 +16483,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
@@ -16716,13 +16514,6 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="11"/>
@@ -16832,7 +16623,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -16982,7 +16773,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -17000,12 +16791,12 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -17547,7 +17338,7 @@
       <c r="C25" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17598,14 +17389,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="36" customHeight="1">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
       <c r="I2" s="7" t="s">
         <v>53</v>
       </c>
@@ -17615,7 +17406,7 @@
         <v>54</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>55</v>
@@ -17627,7 +17418,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="9"/>
       <c r="I3" s="51" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="36" customHeight="1">
@@ -17635,7 +17426,7 @@
         <v>57</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>58</v>
@@ -17647,7 +17438,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="9"/>
       <c r="I4" s="51" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="36" customHeight="1">
@@ -17655,7 +17446,7 @@
         <v>60</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>61</v>
@@ -17667,7 +17458,7 @@
       <c r="G5" s="11"/>
       <c r="H5" s="9"/>
       <c r="I5" s="51" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="36" customHeight="1">
@@ -17675,7 +17466,7 @@
         <v>63</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>64</v>
@@ -17695,7 +17486,7 @@
         <v>67</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>68</v>
@@ -17707,7 +17498,7 @@
       <c r="G7" s="11"/>
       <c r="H7" s="9"/>
       <c r="I7" s="51" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" customHeight="1">
@@ -17715,7 +17506,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>71</v>
@@ -17731,14 +17522,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
       <c r="I9" s="7" t="s">
         <v>74</v>
       </c>
@@ -17754,7 +17545,7 @@
         <v>77</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="11"/>
@@ -17793,7 +17584,7 @@
         <v>85</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>451</v>
+        <v>497</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="13"/>
@@ -17802,14 +17593,14 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1">
-      <c r="A13" s="57"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
+      <c r="A13" s="58"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
       <c r="I13" s="7" t="s">
         <v>87</v>
       </c>
@@ -17935,14 +17726,14 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="36" customHeight="1">
-      <c r="A20" s="57"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
+      <c r="A20" s="58"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
       <c r="I20" s="7" t="s">
         <v>112</v>
       </c>
@@ -17955,7 +17746,7 @@
         <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>115</v>
@@ -17980,7 +17771,7 @@
         <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>121</v>
@@ -18003,7 +17794,7 @@
         <v>125</v>
       </c>
       <c r="C23" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>126</v>
@@ -18024,7 +17815,7 @@
         <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>130</v>
@@ -18045,7 +17836,7 @@
         <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>134</v>
@@ -18066,7 +17857,7 @@
         <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>138</v>
@@ -18089,7 +17880,7 @@
         <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D27" s="25" t="s">
         <v>143</v>
@@ -18112,7 +17903,7 @@
         <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>148</v>
@@ -18133,7 +17924,7 @@
         <v>151</v>
       </c>
       <c r="C29" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>152</v>
@@ -18154,7 +17945,7 @@
         <v>155</v>
       </c>
       <c r="C30" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>156</v>
@@ -18177,7 +17968,7 @@
         <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>161</v>
@@ -18198,7 +17989,7 @@
         <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>165</v>
@@ -18223,7 +18014,7 @@
         <v>170</v>
       </c>
       <c r="C33" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>171</v>
@@ -18248,7 +18039,7 @@
         <v>176</v>
       </c>
       <c r="C34" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>177</v>
@@ -18271,7 +18062,7 @@
         <v>181</v>
       </c>
       <c r="C35" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>182</v>
@@ -18294,7 +18085,7 @@
         <v>186</v>
       </c>
       <c r="C36" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>187</v>
@@ -18317,7 +18108,7 @@
         <v>191</v>
       </c>
       <c r="C37" t="s">
-        <v>459</v>
+        <v>499</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>192</v>
@@ -18331,14 +18122,14 @@
       <c r="I37" s="22"/>
     </row>
     <row r="38" spans="1:9" ht="36" customHeight="1">
-      <c r="A38" s="57"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="59"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
+      <c r="A38" s="58"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
       <c r="I38" s="7" t="s">
         <v>194</v>
       </c>
@@ -18589,7 +18380,7 @@
         <v>248</v>
       </c>
       <c r="F51" s="24" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G51" s="20" t="s">
         <v>249</v>
@@ -18618,14 +18409,14 @@
       <c r="I52" s="22"/>
     </row>
     <row r="53" spans="1:9" ht="36" customHeight="1">
-      <c r="A53" s="57"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="59"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
       <c r="I53" s="7" t="s">
         <v>255</v>
       </c>
@@ -18638,7 +18429,7 @@
         <v>257</v>
       </c>
       <c r="C54" t="s">
-        <v>453</v>
+        <v>500</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>258</v>
@@ -18661,7 +18452,7 @@
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>12</v>
@@ -18684,7 +18475,7 @@
         <v>264</v>
       </c>
       <c r="C56" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>265</v>
@@ -18707,7 +18498,7 @@
         <v>269</v>
       </c>
       <c r="C57" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>270</v>
@@ -18730,7 +18521,7 @@
         <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>275</v>
@@ -18751,7 +18542,7 @@
         <v>277</v>
       </c>
       <c r="C59" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>278</v>
@@ -18774,7 +18565,7 @@
         <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>283</v>
@@ -18795,7 +18586,7 @@
         <v>286</v>
       </c>
       <c r="C61" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>287</v>
@@ -18818,7 +18609,7 @@
         <v>291</v>
       </c>
       <c r="C62" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>292</v>
@@ -18834,14 +18625,14 @@
       <c r="I62" s="31"/>
     </row>
     <row r="63" spans="1:9" ht="36" customHeight="1">
-      <c r="A63" s="57"/>
-      <c r="B63" s="58"/>
-      <c r="C63" s="59"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
+      <c r="A63" s="58"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
       <c r="I63" s="7" t="s">
         <v>295</v>
       </c>
@@ -18854,7 +18645,7 @@
         <v>297</v>
       </c>
       <c r="C64" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>298</v>
@@ -18877,13 +18668,13 @@
         <v>301</v>
       </c>
       <c r="C65" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>302</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="F65" s="34"/>
       <c r="G65" s="11"/>
@@ -18898,13 +18689,13 @@
         <v>304</v>
       </c>
       <c r="C66" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>305</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="F66" s="34"/>
       <c r="G66" s="11"/>
@@ -18919,17 +18710,17 @@
         <v>307</v>
       </c>
       <c r="C67" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>308</v>
       </c>
       <c r="E67" s="53" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F67" s="34"/>
       <c r="G67" s="26" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="H67" s="34"/>
       <c r="I67" s="34" t="s">
@@ -18944,13 +18735,13 @@
         <v>311</v>
       </c>
       <c r="C68" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>312</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="F68" s="34"/>
       <c r="G68" s="11"/>
@@ -18965,13 +18756,13 @@
         <v>314</v>
       </c>
       <c r="C69" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>315</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="F69" s="34"/>
       <c r="G69" s="11"/>
@@ -18986,13 +18777,13 @@
         <v>317</v>
       </c>
       <c r="C70" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>318</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F70" s="34"/>
       <c r="G70" s="11"/>
@@ -19007,13 +18798,13 @@
         <v>320</v>
       </c>
       <c r="C71" t="s">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>321</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="F71" s="34"/>
       <c r="G71" s="11"/>
@@ -19028,13 +18819,13 @@
         <v>323</v>
       </c>
       <c r="C72" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>324</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="F72" s="34"/>
       <c r="G72" s="11"/>
@@ -19042,14 +18833,14 @@
       <c r="I72" s="34"/>
     </row>
     <row r="73" spans="1:9" ht="36" customHeight="1">
-      <c r="A73" s="57"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="59"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
+      <c r="A73" s="58"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="59"/>
       <c r="I73" s="7" t="s">
         <v>325</v>
       </c>
@@ -19065,7 +18856,7 @@
         <v>327</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="F74" s="34"/>
       <c r="G74" s="11"/>
@@ -19083,7 +18874,7 @@
         <v>330</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="F75" s="34"/>
       <c r="G75" s="11"/>
@@ -19101,7 +18892,7 @@
         <v>333</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="F76" s="34"/>
       <c r="G76" s="11"/>
@@ -19119,7 +18910,7 @@
         <v>336</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="F77" s="34"/>
       <c r="G77" s="11"/>
@@ -19137,7 +18928,7 @@
         <v>339</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="F78" s="34"/>
       <c r="G78" s="11"/>
@@ -19155,7 +18946,7 @@
         <v>341</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F79" s="34"/>
       <c r="G79" s="11"/>
@@ -19163,14 +18954,14 @@
       <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:9" ht="36" customHeight="1">
-      <c r="A80" s="57"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="59"/>
-      <c r="D80" s="58"/>
-      <c r="E80" s="58"/>
-      <c r="F80" s="58"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="58"/>
+      <c r="A80" s="58"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
       <c r="I80" s="7" t="s">
         <v>342</v>
       </c>
@@ -19183,7 +18974,7 @@
         <v>344</v>
       </c>
       <c r="C81" t="s">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>345</v>
@@ -19205,14 +18996,14 @@
       <c r="B82" s="36" t="s">
         <v>348</v>
       </c>
-      <c r="C82" s="60" t="s">
-        <v>510</v>
+      <c r="C82" s="57" t="s">
+        <v>505</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>349</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="F82" s="36"/>
       <c r="G82" s="11"/>
@@ -19226,14 +19017,14 @@
       <c r="B83" s="36" t="s">
         <v>351</v>
       </c>
-      <c r="C83" s="60" t="s">
-        <v>510</v>
+      <c r="C83" s="57" t="s">
+        <v>505</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>352</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="F83" s="36"/>
       <c r="G83" s="11"/>
@@ -19247,14 +19038,14 @@
       <c r="B84" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="C84" s="60" t="s">
-        <v>510</v>
+      <c r="C84" s="57" t="s">
+        <v>505</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>355</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="F84" s="36"/>
       <c r="G84" s="11"/>
@@ -19262,14 +19053,14 @@
       <c r="I84" s="36"/>
     </row>
     <row r="85" spans="1:9" ht="36" customHeight="1">
-      <c r="A85" s="57"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="59"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58"/>
+      <c r="A85" s="58"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59"/>
       <c r="I85" s="7" t="s">
         <v>356</v>
       </c>
@@ -19282,7 +19073,7 @@
         <v>358</v>
       </c>
       <c r="C86" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>359</v>
@@ -19305,19 +19096,19 @@
         <v>362</v>
       </c>
       <c r="C87" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>246</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="H87" s="38"/>
       <c r="I87" s="38"/>
@@ -19330,13 +19121,13 @@
         <v>364</v>
       </c>
       <c r="C88" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>365</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="F88" s="38"/>
       <c r="G88" s="11"/>
@@ -19351,13 +19142,13 @@
         <v>367</v>
       </c>
       <c r="C89" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>368</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="F89" s="38"/>
       <c r="G89" s="11"/>
@@ -19372,13 +19163,13 @@
         <v>370</v>
       </c>
       <c r="C90" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>371</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="F90" s="38"/>
       <c r="G90" s="11"/>
@@ -19393,13 +19184,13 @@
         <v>373</v>
       </c>
       <c r="C91" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>374</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="F91" s="38"/>
       <c r="G91" s="11"/>
@@ -19414,13 +19205,13 @@
         <v>376</v>
       </c>
       <c r="C92" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>377</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="F92" s="38"/>
       <c r="G92" s="11"/>
@@ -19435,13 +19226,13 @@
         <v>379</v>
       </c>
       <c r="C93" t="s">
-        <v>462</v>
+        <v>507</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>380</v>
       </c>
       <c r="E93" s="55" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="F93" s="38"/>
       <c r="G93" s="11"/>
@@ -19451,14 +19242,14 @@
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1">
-      <c r="A94" s="57"/>
-      <c r="B94" s="58"/>
-      <c r="C94" s="59"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58"/>
+      <c r="A94" s="58"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="60"/>
+      <c r="D94" s="59"/>
+      <c r="E94" s="59"/>
+      <c r="F94" s="59"/>
+      <c r="G94" s="59"/>
+      <c r="H94" s="59"/>
       <c r="I94" s="7" t="s">
         <v>382</v>
       </c>
@@ -19474,7 +19265,7 @@
         <v>385</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="F95" s="38"/>
       <c r="G95" s="11"/>
@@ -19492,7 +19283,7 @@
         <v>388</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="F96" s="38"/>
       <c r="G96" s="11"/>
@@ -19510,13 +19301,13 @@
         <v>390</v>
       </c>
       <c r="E97" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="F97" s="54" t="s">
+        <v>478</v>
+      </c>
+      <c r="G97" s="26" t="s">
         <v>487</v>
-      </c>
-      <c r="F97" s="54" t="s">
-        <v>490</v>
-      </c>
-      <c r="G97" s="26" t="s">
-        <v>499</v>
       </c>
       <c r="H97" s="38"/>
       <c r="I97" s="38"/>
@@ -19532,7 +19323,7 @@
         <v>393</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="F98" s="38"/>
       <c r="G98" s="11"/>
@@ -19550,7 +19341,7 @@
         <v>396</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="F99" s="38"/>
       <c r="G99" s="11"/>
@@ -19568,7 +19359,7 @@
         <v>398</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="F100" s="38"/>
       <c r="G100" s="11"/>
@@ -19586,7 +19377,7 @@
         <v>401</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="F101" s="38"/>
       <c r="G101" s="11"/>
@@ -19604,7 +19395,7 @@
         <v>403</v>
       </c>
       <c r="E102" s="26" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="F102" s="38"/>
       <c r="G102" s="11"/>
@@ -19622,7 +19413,7 @@
         <v>406</v>
       </c>
       <c r="E103" s="26" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="F103" s="38"/>
       <c r="G103" s="11"/>
@@ -19640,7 +19431,7 @@
         <v>409</v>
       </c>
       <c r="E104" s="26" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="F104" s="38"/>
       <c r="G104" s="11"/>
@@ -19658,7 +19449,7 @@
         <v>412</v>
       </c>
       <c r="E105" s="26" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="F105" s="38"/>
       <c r="G105" s="11"/>
@@ -19666,14 +19457,14 @@
       <c r="I105" s="38"/>
     </row>
     <row r="106" spans="1:9" ht="36" customHeight="1">
-      <c r="A106" s="57"/>
-      <c r="B106" s="58"/>
-      <c r="C106" s="59"/>
-      <c r="D106" s="58"/>
-      <c r="E106" s="58"/>
-      <c r="F106" s="58"/>
-      <c r="G106" s="58"/>
-      <c r="H106" s="58"/>
+      <c r="A106" s="58"/>
+      <c r="B106" s="59"/>
+      <c r="C106" s="60"/>
+      <c r="D106" s="59"/>
+      <c r="E106" s="59"/>
+      <c r="F106" s="59"/>
+      <c r="G106" s="59"/>
+      <c r="H106" s="59"/>
       <c r="I106" s="7" t="s">
         <v>413</v>
       </c>
@@ -19686,10 +19477,10 @@
         <v>415</v>
       </c>
       <c r="C107" t="s">
-        <v>458</v>
+        <v>508</v>
       </c>
       <c r="D107" s="25" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E107" s="40" t="s">
         <v>416</v>
@@ -19709,22 +19500,22 @@
         <v>418</v>
       </c>
       <c r="C108" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>239</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="F108" s="56" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="H108" s="56" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="I108" s="40"/>
     </row>
@@ -19736,13 +19527,13 @@
         <v>420</v>
       </c>
       <c r="C109" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>421</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="F109" s="40"/>
       <c r="G109" s="11"/>
@@ -19757,13 +19548,13 @@
         <v>423</v>
       </c>
       <c r="C110" t="s">
-        <v>463</v>
+        <v>509</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>424</v>
       </c>
       <c r="E110" s="26" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="F110" s="40"/>
       <c r="G110" s="11"/>
@@ -19772,11 +19563,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A94:H94"/>
     <mergeCell ref="A106:H106"/>
     <mergeCell ref="A53:H53"/>
@@ -19784,8 +19570,13 @@
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A85:H85"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="I3" r:id="rId1" xr:uid="{3E973F3D-7F90-47C5-BA46-CD1485089CF1}"/>
     <hyperlink ref="I4" r:id="rId2" xr:uid="{A5A5C564-C1F4-433B-911C-EAC646805F5F}"/>
@@ -19960,7 +19751,7 @@
       <c r="C14" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/LINE_Bot_內容對照表.xlsx
+++ b/LINE_Bot_內容對照表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188F4A14-A296-4061-AC52-35AB68F19DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086F958D-D165-453E-9DB7-A33960FFC99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -222,12 +222,6 @@
     <t>RM-4</t>
   </si>
   <si>
-    <t>臉書粉專</t>
-  </si>
-  <si>
-    <t>【連結】Facebook粉絲專頁</t>
-  </si>
-  <si>
     <t>外部連結，填入URL</t>
   </si>
   <si>
@@ -11396,10 +11390,6 @@
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>臉書粉專</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
     <t>https://sinhu.land.hsinchu.gov.tw/content/?parent_id=10338&amp;type_id=10338</t>
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
@@ -16340,12 +16330,64 @@
   <si>
     <t>檔案應用底圖.jpg</t>
   </si>
+  <si>
+    <t>AI助理</t>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF37474F"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>助理</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>【連結】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>助理</t>
+    </r>
+    <phoneticPr fontId="22" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16523,6 +16565,19 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF37474F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -16625,7 +16680,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -16797,6 +16852,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -17406,7 +17467,7 @@
         <v>54</v>
       </c>
       <c r="B3" s="52" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>55</v>
@@ -17418,7 +17479,7 @@
       <c r="G3" s="11"/>
       <c r="H3" s="9"/>
       <c r="I3" s="51" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="36" customHeight="1">
@@ -17426,7 +17487,7 @@
         <v>57</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>58</v>
@@ -17438,7 +17499,7 @@
       <c r="G4" s="11"/>
       <c r="H4" s="9"/>
       <c r="I4" s="51" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="36" customHeight="1">
@@ -17446,7 +17507,7 @@
         <v>60</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>61</v>
@@ -17458,7 +17519,7 @@
       <c r="G5" s="11"/>
       <c r="H5" s="9"/>
       <c r="I5" s="51" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="36" customHeight="1">
@@ -17466,59 +17527,59 @@
         <v>63</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>457</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>65</v>
+        <v>507</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>508</v>
+      </c>
+      <c r="E6" s="62" t="s">
+        <v>509</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="11"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="36" customHeight="1">
       <c r="A7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>458</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>461</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="11"/>
       <c r="H7" s="9"/>
       <c r="I7" s="51" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" customHeight="1">
       <c r="A8" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>70</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>459</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="F8" s="9"/>
       <c r="G8" s="11"/>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="36" customHeight="1">
@@ -17531,65 +17592,65 @@
       <c r="G9" s="59"/>
       <c r="H9" s="59"/>
       <c r="I9" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="184.5" customHeight="1">
       <c r="A10" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>77</v>
-      </c>
       <c r="E10" s="15" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F10" s="13"/>
       <c r="G10" s="11"/>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="84" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D11" s="10"/>
       <c r="E11" s="15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F11" s="13"/>
       <c r="G11" s="11"/>
       <c r="H11" s="13"/>
       <c r="I11" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="118.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G12" s="11"/>
       <c r="H12" s="13"/>
       <c r="I12" s="14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1">
@@ -17602,127 +17663,127 @@
       <c r="G13" s="59"/>
       <c r="H13" s="59"/>
       <c r="I13" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="36" customHeight="1">
       <c r="A14" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="E14" s="18" t="s">
         <v>89</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>91</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="11"/>
       <c r="H14" s="13"/>
       <c r="I14" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="54.75" customHeight="1">
       <c r="A15" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="E15" s="15" t="s">
         <v>94</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>96</v>
       </c>
       <c r="F15" s="13"/>
       <c r="G15" s="11"/>
       <c r="H15" s="13"/>
       <c r="I15" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="36" customHeight="1">
       <c r="A16" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="E16" s="20" t="s">
         <v>98</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>100</v>
       </c>
       <c r="F16" s="13"/>
       <c r="G16" s="11"/>
       <c r="H16" s="13"/>
       <c r="I16" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="36" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>55</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F17" s="13"/>
       <c r="G17" s="11"/>
       <c r="H17" s="13"/>
       <c r="I17" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="36" customHeight="1">
       <c r="A18" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="E18" s="15" t="s">
         <v>105</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>107</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="11"/>
       <c r="H18" s="13"/>
       <c r="I18" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="36" customHeight="1">
       <c r="A19" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="E19" s="20" t="s">
         <v>109</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>111</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="11"/>
       <c r="H19" s="13"/>
       <c r="I19" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="36" customHeight="1">
@@ -17735,52 +17796,52 @@
       <c r="G20" s="59"/>
       <c r="H20" s="59"/>
       <c r="I20" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="36" customHeight="1">
       <c r="A21" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" t="s">
+        <v>495</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>114</v>
-      </c>
-      <c r="C21" t="s">
-        <v>498</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>116</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H21" s="22"/>
       <c r="I21" s="22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="36" customHeight="1">
       <c r="A22" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>496</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="E22" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="C22" t="s">
-        <v>499</v>
-      </c>
-      <c r="D22" s="23" t="s">
+      <c r="F22" s="24" t="s">
         <v>121</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>123</v>
       </c>
       <c r="G22" s="11"/>
       <c r="H22" s="22"/>
@@ -17788,19 +17849,19 @@
     </row>
     <row r="23" spans="1:9" ht="36" customHeight="1">
       <c r="A23" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" t="s">
+        <v>496</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="E23" s="20" t="s">
         <v>125</v>
-      </c>
-      <c r="C23" t="s">
-        <v>499</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>127</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="11"/>
@@ -17809,19 +17870,19 @@
     </row>
     <row r="24" spans="1:9" ht="36" customHeight="1">
       <c r="A24" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" t="s">
+        <v>496</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="E24" s="20" t="s">
         <v>129</v>
-      </c>
-      <c r="C24" t="s">
-        <v>499</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>131</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="11"/>
@@ -17830,19 +17891,19 @@
     </row>
     <row r="25" spans="1:9" ht="36" customHeight="1">
       <c r="A25" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="E25" s="20" t="s">
         <v>133</v>
-      </c>
-      <c r="C25" t="s">
-        <v>499</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>135</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="11"/>
@@ -17851,22 +17912,22 @@
     </row>
     <row r="26" spans="1:9" ht="36" customHeight="1">
       <c r="A26" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="C26" t="s">
+        <v>496</v>
+      </c>
+      <c r="D26" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="E26" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C26" t="s">
-        <v>499</v>
-      </c>
-      <c r="D26" s="23" t="s">
+      <c r="F26" s="24" t="s">
         <v>138</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>140</v>
       </c>
       <c r="G26" s="11"/>
       <c r="H26" s="22"/>
@@ -17874,22 +17935,22 @@
     </row>
     <row r="27" spans="1:9" ht="36" customHeight="1">
       <c r="A27" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" t="s">
+        <v>496</v>
+      </c>
+      <c r="D27" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="E27" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="C27" t="s">
-        <v>499</v>
-      </c>
-      <c r="D27" s="25" t="s">
+      <c r="F27" s="24" t="s">
         <v>143</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>145</v>
       </c>
       <c r="G27" s="11"/>
       <c r="H27" s="22"/>
@@ -17897,19 +17958,19 @@
     </row>
     <row r="28" spans="1:9" ht="36" customHeight="1">
       <c r="A28" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" t="s">
+        <v>496</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="22" t="s">
+      <c r="E28" s="26" t="s">
         <v>147</v>
-      </c>
-      <c r="C28" t="s">
-        <v>499</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>149</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="11"/>
@@ -17918,19 +17979,19 @@
     </row>
     <row r="29" spans="1:9" ht="36" customHeight="1">
       <c r="A29" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" t="s">
+        <v>496</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="E29" s="20" t="s">
         <v>151</v>
-      </c>
-      <c r="C29" t="s">
-        <v>499</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>153</v>
       </c>
       <c r="F29" s="22"/>
       <c r="G29" s="11"/>
@@ -17939,42 +18000,42 @@
     </row>
     <row r="30" spans="1:9" ht="36" customHeight="1">
       <c r="A30" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>496</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="22" t="s">
+      <c r="E30" s="27" t="s">
         <v>155</v>
-      </c>
-      <c r="C30" t="s">
-        <v>499</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>157</v>
       </c>
       <c r="F30" s="22"/>
       <c r="G30" s="11"/>
       <c r="H30" s="22"/>
       <c r="I30" s="22" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="36" customHeight="1">
       <c r="A31" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" t="s">
+        <v>496</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="E31" s="26" t="s">
         <v>160</v>
-      </c>
-      <c r="C31" t="s">
-        <v>499</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>162</v>
       </c>
       <c r="F31" s="22"/>
       <c r="G31" s="11"/>
@@ -17983,72 +18044,72 @@
     </row>
     <row r="32" spans="1:9" ht="36" customHeight="1">
       <c r="A32" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s">
+        <v>496</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="E32" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C32" t="s">
-        <v>499</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="F32" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="G32" s="26" t="s">
         <v>166</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="G32" s="26" t="s">
-        <v>168</v>
       </c>
       <c r="H32" s="22"/>
       <c r="I32" s="22"/>
     </row>
     <row r="33" spans="1:9" ht="36" customHeight="1">
       <c r="A33" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" t="s">
+        <v>496</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="E33" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C33" t="s">
-        <v>499</v>
-      </c>
-      <c r="D33" s="10" t="s">
+      <c r="F33" s="24" t="s">
         <v>171</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>173</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="36" customHeight="1">
       <c r="A34" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" t="s">
+        <v>496</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="E34" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="C34" t="s">
-        <v>499</v>
-      </c>
-      <c r="D34" s="10" t="s">
+      <c r="F34" s="24" t="s">
         <v>177</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>179</v>
       </c>
       <c r="G34" s="11"/>
       <c r="H34" s="22"/>
@@ -18056,22 +18117,22 @@
     </row>
     <row r="35" spans="1:9" ht="36" customHeight="1">
       <c r="A35" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C35" t="s">
+        <v>496</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="E35" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C35" t="s">
-        <v>499</v>
-      </c>
-      <c r="D35" s="10" t="s">
+      <c r="F35" s="24" t="s">
         <v>182</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="F35" s="24" t="s">
-        <v>184</v>
       </c>
       <c r="G35" s="11"/>
       <c r="H35" s="22"/>
@@ -18079,22 +18140,22 @@
     </row>
     <row r="36" spans="1:9" ht="36" customHeight="1">
       <c r="A36" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" t="s">
+        <v>496</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="E36" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C36" t="s">
-        <v>499</v>
-      </c>
-      <c r="D36" s="10" t="s">
+      <c r="F36" s="24" t="s">
         <v>187</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>189</v>
       </c>
       <c r="G36" s="11"/>
       <c r="H36" s="22"/>
@@ -18102,19 +18163,19 @@
     </row>
     <row r="37" spans="1:9" ht="36" customHeight="1">
       <c r="A37" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="C37" t="s">
+        <v>496</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="E37" s="20" t="s">
         <v>191</v>
-      </c>
-      <c r="C37" t="s">
-        <v>499</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>193</v>
       </c>
       <c r="F37" s="22"/>
       <c r="G37" s="11"/>
@@ -18131,61 +18192,61 @@
       <c r="G38" s="59"/>
       <c r="H38" s="59"/>
       <c r="I38" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="36" customHeight="1">
       <c r="A39" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="E39" s="27" t="s">
         <v>196</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>198</v>
       </c>
       <c r="F39" s="22"/>
       <c r="G39" s="11"/>
       <c r="H39" s="22"/>
       <c r="I39" s="22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="36" customHeight="1">
       <c r="A40" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="E40" s="20" t="s">
         <v>201</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>202</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>203</v>
       </c>
       <c r="F40" s="22"/>
       <c r="G40" s="11"/>
       <c r="H40" s="22"/>
       <c r="I40" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="36" customHeight="1">
       <c r="A41" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B41" s="22" t="s">
+      <c r="E41" s="20" t="s">
         <v>206</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>208</v>
       </c>
       <c r="F41" s="22"/>
       <c r="G41" s="11"/>
@@ -18194,16 +18255,16 @@
     </row>
     <row r="42" spans="1:9" ht="36" customHeight="1">
       <c r="A42" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="E42" s="20" t="s">
         <v>210</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>212</v>
       </c>
       <c r="F42" s="22"/>
       <c r="G42" s="11"/>
@@ -18212,36 +18273,36 @@
     </row>
     <row r="43" spans="1:9" ht="36" customHeight="1">
       <c r="A43" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B43" s="22" t="s">
+      <c r="E43" s="20" t="s">
         <v>214</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>216</v>
       </c>
       <c r="F43" s="22"/>
       <c r="G43" s="20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H43" s="22"/>
       <c r="I43" s="22"/>
     </row>
     <row r="44" spans="1:9" ht="36" customHeight="1">
       <c r="A44" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B44" s="22" t="s">
+      <c r="E44" s="20" t="s">
         <v>219</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>221</v>
       </c>
       <c r="F44" s="22"/>
       <c r="G44" s="11"/>
@@ -18250,16 +18311,16 @@
     </row>
     <row r="45" spans="1:9" ht="36" customHeight="1">
       <c r="A45" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B45" s="22" t="s">
+      <c r="E45" s="20" t="s">
         <v>223</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>225</v>
       </c>
       <c r="F45" s="22"/>
       <c r="G45" s="11"/>
@@ -18268,16 +18329,16 @@
     </row>
     <row r="46" spans="1:9" ht="36" customHeight="1">
       <c r="A46" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B46" s="22" t="s">
+      <c r="E46" s="20" t="s">
         <v>227</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>229</v>
       </c>
       <c r="F46" s="22"/>
       <c r="G46" s="11"/>
@@ -18286,16 +18347,16 @@
     </row>
     <row r="47" spans="1:9" ht="36" customHeight="1">
       <c r="A47" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B47" s="22" t="s">
+      <c r="E47" s="20" t="s">
         <v>231</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>233</v>
       </c>
       <c r="F47" s="22"/>
       <c r="G47" s="11"/>
@@ -18304,19 +18365,19 @@
     </row>
     <row r="48" spans="1:9" ht="36" customHeight="1">
       <c r="A48" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B48" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="F48" s="24" t="s">
         <v>171</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="F48" s="24" t="s">
-        <v>173</v>
       </c>
       <c r="G48" s="11"/>
       <c r="H48" s="22"/>
@@ -18324,19 +18385,19 @@
     </row>
     <row r="49" spans="1:9" ht="36" customHeight="1">
       <c r="A49" s="21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B49" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="F49" s="24" t="s">
         <v>177</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49" s="24" t="s">
-        <v>179</v>
       </c>
       <c r="G49" s="11"/>
       <c r="H49" s="22"/>
@@ -18344,65 +18405,65 @@
     </row>
     <row r="50" spans="1:9" ht="36" customHeight="1">
       <c r="A50" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B50" s="22" t="s">
+      <c r="E50" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="F50" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="G50" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="F50" s="24" t="s">
+      <c r="H50" s="28" t="s">
         <v>242</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>243</v>
-      </c>
-      <c r="H50" s="28" t="s">
-        <v>244</v>
       </c>
       <c r="I50" s="22"/>
     </row>
     <row r="51" spans="1:9" ht="36" customHeight="1">
       <c r="A51" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B51" s="22" t="s">
+      <c r="E51" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="F51" s="24" t="s">
+        <v>474</v>
+      </c>
+      <c r="G51" s="20" t="s">
         <v>247</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="F51" s="24" t="s">
-        <v>477</v>
-      </c>
-      <c r="G51" s="20" t="s">
-        <v>249</v>
       </c>
       <c r="H51" s="22"/>
       <c r="I51" s="22"/>
     </row>
     <row r="52" spans="1:9" ht="36" customHeight="1">
       <c r="A52" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B52" s="22" t="s">
+      <c r="E52" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="F52" s="29" t="s">
         <v>252</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="F52" s="29" t="s">
-        <v>254</v>
       </c>
       <c r="G52" s="11"/>
       <c r="H52" s="22"/>
@@ -18418,50 +18479,50 @@
       <c r="G53" s="59"/>
       <c r="H53" s="59"/>
       <c r="I53" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="36" customHeight="1">
       <c r="A54" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="C54" t="s">
+        <v>497</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B54" s="31" t="s">
+      <c r="E54" s="31" t="s">
         <v>257</v>
-      </c>
-      <c r="C54" t="s">
-        <v>500</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="E54" s="31" t="s">
-        <v>259</v>
       </c>
       <c r="F54" s="31"/>
       <c r="G54" s="11"/>
       <c r="H54" s="31"/>
       <c r="I54" s="31" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="36" customHeight="1">
       <c r="A55" s="30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>12</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F55" s="32" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G55" s="11"/>
       <c r="H55" s="31"/>
@@ -18469,22 +18530,22 @@
     </row>
     <row r="56" spans="1:9" ht="36" customHeight="1">
       <c r="A56" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="C56" t="s">
+        <v>498</v>
+      </c>
+      <c r="D56" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="B56" s="31" t="s">
+      <c r="E56" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="C56" t="s">
-        <v>501</v>
-      </c>
-      <c r="D56" s="10" t="s">
+      <c r="F56" s="32" t="s">
         <v>265</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="F56" s="32" t="s">
-        <v>267</v>
       </c>
       <c r="G56" s="11"/>
       <c r="H56" s="31"/>
@@ -18492,42 +18553,42 @@
     </row>
     <row r="57" spans="1:9" ht="36" customHeight="1">
       <c r="A57" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" t="s">
+        <v>498</v>
+      </c>
+      <c r="D57" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B57" s="31" t="s">
+      <c r="E57" s="20" t="s">
         <v>269</v>
-      </c>
-      <c r="C57" t="s">
-        <v>501</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>271</v>
       </c>
       <c r="F57" s="31"/>
       <c r="G57" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H57" s="31"/>
       <c r="I57" s="31"/>
     </row>
     <row r="58" spans="1:9" ht="36" customHeight="1">
       <c r="A58" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C58" t="s">
+        <v>498</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B58" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="C58" t="s">
-        <v>501</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>275</v>
-      </c>
       <c r="E58" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F58" s="31"/>
       <c r="G58" s="11"/>
@@ -18536,22 +18597,22 @@
     </row>
     <row r="59" spans="1:9" ht="36" customHeight="1">
       <c r="A59" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="C59" t="s">
+        <v>498</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B59" s="31" t="s">
+      <c r="E59" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="C59" t="s">
-        <v>501</v>
-      </c>
-      <c r="D59" s="10" t="s">
+      <c r="F59" s="32" t="s">
         <v>278</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="F59" s="32" t="s">
-        <v>280</v>
       </c>
       <c r="G59" s="11"/>
       <c r="H59" s="31"/>
@@ -18559,19 +18620,19 @@
     </row>
     <row r="60" spans="1:9" ht="36" customHeight="1">
       <c r="A60" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C60" t="s">
+        <v>498</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B60" s="31" t="s">
+      <c r="E60" s="20" t="s">
         <v>282</v>
-      </c>
-      <c r="C60" t="s">
-        <v>501</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>284</v>
       </c>
       <c r="F60" s="31"/>
       <c r="G60" s="11"/>
@@ -18580,22 +18641,22 @@
     </row>
     <row r="61" spans="1:9" ht="36" customHeight="1">
       <c r="A61" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C61" t="s">
+        <v>498</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B61" s="31" t="s">
+      <c r="E61" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C61" t="s">
-        <v>501</v>
-      </c>
-      <c r="D61" s="10" t="s">
+      <c r="F61" s="32" t="s">
         <v>287</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="F61" s="32" t="s">
-        <v>289</v>
       </c>
       <c r="G61" s="11"/>
       <c r="H61" s="31"/>
@@ -18603,22 +18664,22 @@
     </row>
     <row r="62" spans="1:9" ht="36" customHeight="1">
       <c r="A62" s="30" t="s">
+        <v>288</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>289</v>
+      </c>
+      <c r="C62" t="s">
+        <v>498</v>
+      </c>
+      <c r="D62" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B62" s="31" t="s">
+      <c r="E62" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="C62" t="s">
-        <v>501</v>
-      </c>
-      <c r="D62" s="10" t="s">
+      <c r="F62" s="32" t="s">
         <v>292</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>294</v>
       </c>
       <c r="G62" s="11"/>
       <c r="H62" s="31"/>
@@ -18634,47 +18695,47 @@
       <c r="G63" s="59"/>
       <c r="H63" s="59"/>
       <c r="I63" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="36" customHeight="1">
       <c r="A64" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="C64" t="s">
+        <v>499</v>
+      </c>
+      <c r="D64" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B64" s="34" t="s">
+      <c r="E64" s="34" t="s">
         <v>297</v>
-      </c>
-      <c r="C64" t="s">
-        <v>502</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="E64" s="34" t="s">
-        <v>299</v>
       </c>
       <c r="F64" s="34"/>
       <c r="G64" s="11"/>
       <c r="H64" s="34"/>
       <c r="I64" s="34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="36" customHeight="1">
       <c r="A65" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="C65" t="s">
+        <v>500</v>
+      </c>
+      <c r="D65" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B65" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="C65" t="s">
-        <v>503</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>302</v>
-      </c>
       <c r="E65" s="26" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F65" s="34"/>
       <c r="G65" s="11"/>
@@ -18683,19 +18744,19 @@
     </row>
     <row r="66" spans="1:9" ht="36" customHeight="1">
       <c r="A66" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="C66" t="s">
+        <v>500</v>
+      </c>
+      <c r="D66" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="B66" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="C66" t="s">
-        <v>503</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>305</v>
-      </c>
       <c r="E66" s="26" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F66" s="34"/>
       <c r="G66" s="11"/>
@@ -18704,44 +18765,44 @@
     </row>
     <row r="67" spans="1:9" ht="36" customHeight="1">
       <c r="A67" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="C67" t="s">
+        <v>500</v>
+      </c>
+      <c r="D67" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B67" s="34" t="s">
-        <v>307</v>
-      </c>
-      <c r="C67" t="s">
-        <v>503</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>308</v>
-      </c>
       <c r="E67" s="53" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F67" s="34"/>
       <c r="G67" s="26" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H67" s="34"/>
       <c r="I67" s="34" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="36" customHeight="1">
       <c r="A68" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="C68" t="s">
+        <v>500</v>
+      </c>
+      <c r="D68" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B68" s="34" t="s">
-        <v>311</v>
-      </c>
-      <c r="C68" t="s">
-        <v>503</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>312</v>
-      </c>
       <c r="E68" s="26" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F68" s="34"/>
       <c r="G68" s="11"/>
@@ -18750,19 +18811,19 @@
     </row>
     <row r="69" spans="1:9" ht="36" customHeight="1">
       <c r="A69" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="C69" t="s">
+        <v>500</v>
+      </c>
+      <c r="D69" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B69" s="34" t="s">
-        <v>314</v>
-      </c>
-      <c r="C69" t="s">
-        <v>503</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>315</v>
-      </c>
       <c r="E69" s="26" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F69" s="34"/>
       <c r="G69" s="11"/>
@@ -18771,19 +18832,19 @@
     </row>
     <row r="70" spans="1:9" ht="36" customHeight="1">
       <c r="A70" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" t="s">
+        <v>500</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B70" s="34" t="s">
-        <v>317</v>
-      </c>
-      <c r="C70" t="s">
-        <v>503</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>318</v>
-      </c>
       <c r="E70" s="26" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F70" s="34"/>
       <c r="G70" s="11"/>
@@ -18792,19 +18853,19 @@
     </row>
     <row r="71" spans="1:9" ht="36" customHeight="1">
       <c r="A71" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="C71" t="s">
+        <v>500</v>
+      </c>
+      <c r="D71" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="B71" s="34" t="s">
-        <v>320</v>
-      </c>
-      <c r="C71" t="s">
-        <v>503</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>321</v>
-      </c>
       <c r="E71" s="26" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F71" s="34"/>
       <c r="G71" s="11"/>
@@ -18813,19 +18874,19 @@
     </row>
     <row r="72" spans="1:9" ht="36" customHeight="1">
       <c r="A72" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" t="s">
+        <v>500</v>
+      </c>
+      <c r="D72" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B72" s="34" t="s">
-        <v>323</v>
-      </c>
-      <c r="C72" t="s">
-        <v>503</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>324</v>
-      </c>
       <c r="E72" s="26" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F72" s="34"/>
       <c r="G72" s="11"/>
@@ -18842,21 +18903,21 @@
       <c r="G73" s="59"/>
       <c r="H73" s="59"/>
       <c r="I73" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="36" customHeight="1">
       <c r="A74" s="33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F74" s="34"/>
       <c r="G74" s="11"/>
@@ -18865,16 +18926,16 @@
     </row>
     <row r="75" spans="1:9" ht="36" customHeight="1">
       <c r="A75" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="D75" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B75" s="34" t="s">
-        <v>329</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>330</v>
-      </c>
       <c r="E75" s="26" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F75" s="34"/>
       <c r="G75" s="11"/>
@@ -18883,16 +18944,16 @@
     </row>
     <row r="76" spans="1:9" ht="36" customHeight="1">
       <c r="A76" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="D76" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B76" s="34" t="s">
-        <v>332</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>333</v>
-      </c>
       <c r="E76" s="26" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F76" s="34"/>
       <c r="G76" s="11"/>
@@ -18901,16 +18962,16 @@
     </row>
     <row r="77" spans="1:9" ht="36" customHeight="1">
       <c r="A77" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="D77" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B77" s="34" t="s">
-        <v>335</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>336</v>
-      </c>
       <c r="E77" s="26" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F77" s="34"/>
       <c r="G77" s="11"/>
@@ -18919,16 +18980,16 @@
     </row>
     <row r="78" spans="1:9" ht="36" customHeight="1">
       <c r="A78" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="D78" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B78" s="34" t="s">
-        <v>338</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>339</v>
-      </c>
       <c r="E78" s="26" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F78" s="34"/>
       <c r="G78" s="11"/>
@@ -18937,16 +18998,16 @@
     </row>
     <row r="79" spans="1:9" ht="36" customHeight="1">
       <c r="A79" s="33" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F79" s="34"/>
       <c r="G79" s="11"/>
@@ -18963,47 +19024,47 @@
       <c r="G80" s="59"/>
       <c r="H80" s="59"/>
       <c r="I80" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="36" customHeight="1">
       <c r="A81" s="35" t="s">
+        <v>341</v>
+      </c>
+      <c r="B81" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C81" t="s">
+        <v>501</v>
+      </c>
+      <c r="D81" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="B81" s="36" t="s">
+      <c r="E81" s="36" t="s">
         <v>344</v>
-      </c>
-      <c r="C81" t="s">
-        <v>504</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="E81" s="36" t="s">
-        <v>346</v>
       </c>
       <c r="F81" s="36"/>
       <c r="G81" s="11"/>
       <c r="H81" s="36"/>
       <c r="I81" s="36" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="36" customHeight="1">
       <c r="A82" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>346</v>
+      </c>
+      <c r="C82" s="57" t="s">
+        <v>502</v>
+      </c>
+      <c r="D82" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="B82" s="36" t="s">
-        <v>348</v>
-      </c>
-      <c r="C82" s="57" t="s">
-        <v>505</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>349</v>
-      </c>
       <c r="E82" s="26" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F82" s="36"/>
       <c r="G82" s="11"/>
@@ -19012,19 +19073,19 @@
     </row>
     <row r="83" spans="1:9" ht="36" customHeight="1">
       <c r="A83" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>349</v>
+      </c>
+      <c r="C83" s="57" t="s">
+        <v>502</v>
+      </c>
+      <c r="D83" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="B83" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="C83" s="57" t="s">
-        <v>505</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>352</v>
-      </c>
       <c r="E83" s="26" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="F83" s="36"/>
       <c r="G83" s="11"/>
@@ -19033,19 +19094,19 @@
     </row>
     <row r="84" spans="1:9" ht="36" customHeight="1">
       <c r="A84" s="35" t="s">
+        <v>351</v>
+      </c>
+      <c r="B84" s="36" t="s">
+        <v>352</v>
+      </c>
+      <c r="C84" s="57" t="s">
+        <v>502</v>
+      </c>
+      <c r="D84" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B84" s="36" t="s">
-        <v>354</v>
-      </c>
-      <c r="C84" s="57" t="s">
-        <v>505</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>355</v>
-      </c>
       <c r="E84" s="26" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F84" s="36"/>
       <c r="G84" s="11"/>
@@ -19062,72 +19123,72 @@
       <c r="G85" s="59"/>
       <c r="H85" s="59"/>
       <c r="I85" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="36" customHeight="1">
       <c r="A86" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="B86" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="C86" t="s">
+        <v>503</v>
+      </c>
+      <c r="D86" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B86" s="38" t="s">
+      <c r="E86" s="38" t="s">
         <v>358</v>
-      </c>
-      <c r="C86" t="s">
-        <v>506</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="E86" s="38" t="s">
-        <v>360</v>
       </c>
       <c r="F86" s="38"/>
       <c r="G86" s="11"/>
       <c r="H86" s="38"/>
       <c r="I86" s="38" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="36" customHeight="1">
       <c r="A87" s="37" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B87" s="38" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C87" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E87" s="26" t="s">
+        <v>472</v>
+      </c>
+      <c r="F87" s="54" t="s">
         <v>475</v>
       </c>
-      <c r="F87" s="54" t="s">
-        <v>478</v>
-      </c>
       <c r="G87" s="26" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="H87" s="38"/>
       <c r="I87" s="38"/>
     </row>
     <row r="88" spans="1:9" ht="36" customHeight="1">
       <c r="A88" s="37" t="s">
+        <v>361</v>
+      </c>
+      <c r="B88" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="C88" t="s">
+        <v>504</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="B88" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="C88" t="s">
-        <v>507</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>365</v>
-      </c>
       <c r="E88" s="26" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F88" s="38"/>
       <c r="G88" s="11"/>
@@ -19136,19 +19197,19 @@
     </row>
     <row r="89" spans="1:9" ht="36" customHeight="1">
       <c r="A89" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="B89" s="38" t="s">
+        <v>365</v>
+      </c>
+      <c r="C89" t="s">
+        <v>504</v>
+      </c>
+      <c r="D89" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="B89" s="38" t="s">
-        <v>367</v>
-      </c>
-      <c r="C89" t="s">
-        <v>507</v>
-      </c>
-      <c r="D89" s="10" t="s">
-        <v>368</v>
-      </c>
       <c r="E89" s="26" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F89" s="38"/>
       <c r="G89" s="11"/>
@@ -19157,19 +19218,19 @@
     </row>
     <row r="90" spans="1:9" ht="36" customHeight="1">
       <c r="A90" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="B90" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="C90" t="s">
+        <v>504</v>
+      </c>
+      <c r="D90" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B90" s="38" t="s">
-        <v>370</v>
-      </c>
-      <c r="C90" t="s">
-        <v>507</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>371</v>
-      </c>
       <c r="E90" s="26" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F90" s="38"/>
       <c r="G90" s="11"/>
@@ -19178,19 +19239,19 @@
     </row>
     <row r="91" spans="1:9" ht="36" customHeight="1">
       <c r="A91" s="37" t="s">
+        <v>370</v>
+      </c>
+      <c r="B91" s="38" t="s">
+        <v>371</v>
+      </c>
+      <c r="C91" t="s">
+        <v>504</v>
+      </c>
+      <c r="D91" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B91" s="38" t="s">
-        <v>373</v>
-      </c>
-      <c r="C91" t="s">
-        <v>507</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>374</v>
-      </c>
       <c r="E91" s="26" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F91" s="38"/>
       <c r="G91" s="11"/>
@@ -19199,19 +19260,19 @@
     </row>
     <row r="92" spans="1:9" ht="36" customHeight="1">
       <c r="A92" s="37" t="s">
+        <v>373</v>
+      </c>
+      <c r="B92" s="38" t="s">
+        <v>374</v>
+      </c>
+      <c r="C92" t="s">
+        <v>504</v>
+      </c>
+      <c r="D92" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B92" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="C92" t="s">
-        <v>507</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>377</v>
-      </c>
       <c r="E92" s="26" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F92" s="38"/>
       <c r="G92" s="11"/>
@@ -19220,25 +19281,25 @@
     </row>
     <row r="93" spans="1:9" ht="36" customHeight="1">
       <c r="A93" s="37" t="s">
+        <v>376</v>
+      </c>
+      <c r="B93" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="C93" t="s">
+        <v>504</v>
+      </c>
+      <c r="D93" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="B93" s="38" t="s">
-        <v>379</v>
-      </c>
-      <c r="C93" t="s">
-        <v>507</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>380</v>
-      </c>
       <c r="E93" s="55" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F93" s="38"/>
       <c r="G93" s="11"/>
       <c r="H93" s="38"/>
       <c r="I93" s="38" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="36" customHeight="1">
@@ -19251,21 +19312,21 @@
       <c r="G94" s="59"/>
       <c r="H94" s="59"/>
       <c r="I94" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="36" customHeight="1">
       <c r="A95" s="37" t="s">
+        <v>381</v>
+      </c>
+      <c r="B95" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="D95" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B95" s="38" t="s">
-        <v>384</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>385</v>
-      </c>
       <c r="E95" s="26" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F95" s="38"/>
       <c r="G95" s="11"/>
@@ -19274,16 +19335,16 @@
     </row>
     <row r="96" spans="1:9" ht="36" customHeight="1">
       <c r="A96" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="B96" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="D96" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="B96" s="38" t="s">
-        <v>387</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>388</v>
-      </c>
       <c r="E96" s="26" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F96" s="38"/>
       <c r="G96" s="11"/>
@@ -19292,38 +19353,38 @@
     </row>
     <row r="97" spans="1:9" ht="36" customHeight="1">
       <c r="A97" s="37" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B97" s="38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E97" s="26" t="s">
+        <v>472</v>
+      </c>
+      <c r="F97" s="54" t="s">
         <v>475</v>
       </c>
-      <c r="F97" s="54" t="s">
-        <v>478</v>
-      </c>
       <c r="G97" s="26" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H97" s="38"/>
       <c r="I97" s="38"/>
     </row>
     <row r="98" spans="1:9" ht="36" customHeight="1">
       <c r="A98" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="B98" s="38" t="s">
+        <v>390</v>
+      </c>
+      <c r="D98" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="B98" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>393</v>
-      </c>
       <c r="E98" s="26" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F98" s="38"/>
       <c r="G98" s="11"/>
@@ -19332,16 +19393,16 @@
     </row>
     <row r="99" spans="1:9" ht="36" customHeight="1">
       <c r="A99" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="B99" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="D99" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B99" s="38" t="s">
-        <v>395</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>396</v>
-      </c>
       <c r="E99" s="26" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F99" s="38"/>
       <c r="G99" s="11"/>
@@ -19350,16 +19411,16 @@
     </row>
     <row r="100" spans="1:9" ht="36" customHeight="1">
       <c r="A100" s="37" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B100" s="38" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F100" s="38"/>
       <c r="G100" s="11"/>
@@ -19368,16 +19429,16 @@
     </row>
     <row r="101" spans="1:9" ht="36" customHeight="1">
       <c r="A101" s="37" t="s">
+        <v>397</v>
+      </c>
+      <c r="B101" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="D101" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B101" s="38" t="s">
-        <v>400</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>401</v>
-      </c>
       <c r="E101" s="26" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F101" s="38"/>
       <c r="G101" s="11"/>
@@ -19386,16 +19447,16 @@
     </row>
     <row r="102" spans="1:9" ht="36" customHeight="1">
       <c r="A102" s="37" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B102" s="38" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E102" s="26" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F102" s="38"/>
       <c r="G102" s="11"/>
@@ -19404,16 +19465,16 @@
     </row>
     <row r="103" spans="1:9" ht="36" customHeight="1">
       <c r="A103" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="B103" s="38" t="s">
+        <v>403</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="B103" s="38" t="s">
-        <v>405</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>406</v>
-      </c>
       <c r="E103" s="26" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F103" s="38"/>
       <c r="G103" s="11"/>
@@ -19422,16 +19483,16 @@
     </row>
     <row r="104" spans="1:9" ht="36" customHeight="1">
       <c r="A104" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="B104" s="38" t="s">
+        <v>406</v>
+      </c>
+      <c r="D104" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="B104" s="38" t="s">
-        <v>408</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>409</v>
-      </c>
       <c r="E104" s="26" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F104" s="38"/>
       <c r="G104" s="11"/>
@@ -19440,16 +19501,16 @@
     </row>
     <row r="105" spans="1:9" ht="36" customHeight="1">
       <c r="A105" s="37" t="s">
+        <v>408</v>
+      </c>
+      <c r="B105" s="38" t="s">
+        <v>409</v>
+      </c>
+      <c r="D105" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="B105" s="38" t="s">
-        <v>411</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>412</v>
-      </c>
       <c r="E105" s="26" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F105" s="38"/>
       <c r="G105" s="11"/>
@@ -19466,74 +19527,74 @@
       <c r="G106" s="59"/>
       <c r="H106" s="59"/>
       <c r="I106" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="36" customHeight="1">
       <c r="A107" s="39" t="s">
+        <v>412</v>
+      </c>
+      <c r="B107" s="40" t="s">
+        <v>413</v>
+      </c>
+      <c r="C107" t="s">
+        <v>505</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>449</v>
+      </c>
+      <c r="E107" s="40" t="s">
         <v>414</v>
-      </c>
-      <c r="B107" s="40" t="s">
-        <v>415</v>
-      </c>
-      <c r="C107" t="s">
-        <v>508</v>
-      </c>
-      <c r="D107" s="25" t="s">
-        <v>451</v>
-      </c>
-      <c r="E107" s="40" t="s">
-        <v>416</v>
       </c>
       <c r="F107" s="40"/>
       <c r="G107" s="11"/>
       <c r="H107" s="40"/>
       <c r="I107" s="40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="36" customHeight="1">
       <c r="A108" s="39" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B108" s="40" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C108" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E108" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="F108" s="56" t="s">
+        <v>490</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>489</v>
+      </c>
+      <c r="H108" s="56" t="s">
         <v>491</v>
-      </c>
-      <c r="F108" s="56" t="s">
-        <v>493</v>
-      </c>
-      <c r="G108" s="26" t="s">
-        <v>492</v>
-      </c>
-      <c r="H108" s="56" t="s">
-        <v>494</v>
       </c>
       <c r="I108" s="40"/>
     </row>
     <row r="109" spans="1:9" ht="36" customHeight="1">
       <c r="A109" s="39" t="s">
+        <v>417</v>
+      </c>
+      <c r="B109" s="40" t="s">
+        <v>418</v>
+      </c>
+      <c r="C109" t="s">
+        <v>506</v>
+      </c>
+      <c r="D109" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="B109" s="40" t="s">
-        <v>420</v>
-      </c>
-      <c r="C109" t="s">
-        <v>509</v>
-      </c>
-      <c r="D109" s="10" t="s">
-        <v>421</v>
-      </c>
       <c r="E109" s="26" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F109" s="40"/>
       <c r="G109" s="11"/>
@@ -19542,19 +19603,19 @@
     </row>
     <row r="110" spans="1:9" ht="36" customHeight="1">
       <c r="A110" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="B110" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="C110" t="s">
+        <v>506</v>
+      </c>
+      <c r="D110" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="B110" s="40" t="s">
-        <v>423</v>
-      </c>
-      <c r="C110" t="s">
-        <v>509</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>424</v>
-      </c>
       <c r="E110" s="26" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F110" s="40"/>
       <c r="G110" s="11"/>
@@ -19563,6 +19624,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A94:H94"/>
     <mergeCell ref="A106:H106"/>
     <mergeCell ref="A53:H53"/>
@@ -19570,11 +19636,6 @@
     <mergeCell ref="A73:H73"/>
     <mergeCell ref="A80:H80"/>
     <mergeCell ref="A85:H85"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:H38"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>
@@ -19599,10 +19660,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21.9" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C1" s="41" t="s">
         <v>2</v>
@@ -19616,133 +19677,133 @@
         <v>6</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21.9" customHeight="1">
       <c r="A3" s="13" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B3" s="43">
         <v>3</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21.9" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B4" s="43">
         <v>6</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.9" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B5" s="44">
         <v>17</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21.9" customHeight="1">
       <c r="A6" s="22" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B6" s="44">
         <v>14</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21.9" customHeight="1">
       <c r="A7" s="31" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B7" s="45">
         <v>9</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21.9" customHeight="1">
       <c r="A8" s="34" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B8" s="46">
         <v>9</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="21.9" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B9" s="46">
         <v>6</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="21.9" customHeight="1">
       <c r="A10" s="36" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B10" s="47">
         <v>4</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="21.9" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B11" s="48">
         <v>8</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="21.9" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B12" s="48">
         <v>11</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="21.9" customHeight="1">
       <c r="A13" s="40" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B13" s="49">
         <v>4</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="21.9" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B14" s="50">
         <f>SUM(B2:B13)</f>
